--- a/Diagram/UseCaseDescription.xlsx
+++ b/Diagram/UseCaseDescription.xlsx
@@ -5,22 +5,22 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/paultsai/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/paultsai/Desktop/SLC/TPA/Desktop/TPA-Desktop/Diagram/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81221705-0D49-D547-98AD-A37B697746E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFB371F4-B3BB-1B46-A87C-4F5B9CF81B83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="80" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="7" xr2:uid="{2183EE87-2FE0-1848-A8EC-EAF6DA5552F2}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="7" xr2:uid="{2183EE87-2FE0-1848-A8EC-EAF6DA5552F2}"/>
   </bookViews>
   <sheets>
-    <sheet name="Add New Menu Item" sheetId="1" r:id="rId1"/>
-    <sheet name="Add Lost and Found Log" sheetId="2" r:id="rId2"/>
-    <sheet name="Update Lost and Found Log" sheetId="3" r:id="rId3"/>
-    <sheet name="Add New Souvenir" sheetId="4" r:id="rId4"/>
-    <sheet name="Buy Souvenir" sheetId="6" r:id="rId5"/>
-    <sheet name="Propose New Store" sheetId="5" r:id="rId6"/>
-    <sheet name="Propose New Restaurants" sheetId="7" r:id="rId7"/>
-    <sheet name="Propose New Rides" sheetId="8" r:id="rId8"/>
+    <sheet name="1. Add New Menu Item" sheetId="1" r:id="rId1"/>
+    <sheet name="2. Add Lost and Found Log" sheetId="2" r:id="rId2"/>
+    <sheet name="3. Update Lost and Found Log" sheetId="3" r:id="rId3"/>
+    <sheet name="4. Add New Souvenir" sheetId="4" r:id="rId4"/>
+    <sheet name="5. Buy Souvenir" sheetId="6" r:id="rId5"/>
+    <sheet name="6. Propose New Store" sheetId="5" r:id="rId6"/>
+    <sheet name="7. Propose New Rides" sheetId="8" r:id="rId7"/>
+    <sheet name="8. Propose Ride Deletion" sheetId="7" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="661" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="301">
   <si>
     <t>Use Case Name:</t>
   </si>
@@ -120,9 +120,6 @@
     <t>3. F&amp;B Supervisor enters the menu item data (picture, name, price)</t>
   </si>
   <si>
-    <t>2.1 The system validates the restaurant exists</t>
-  </si>
-  <si>
     <t>3.1 The system validates that the picture is not corrupted</t>
   </si>
   <si>
@@ -265,9 +262,6 @@
     <t>2.7 The database connection is severed</t>
   </si>
   <si>
-    <t>1.3 Loads in the form with the current log data</t>
-  </si>
-  <si>
     <t>View Lost and Found Items Log, Send Customer Notification</t>
   </si>
   <si>
@@ -281,9 +275,6 @@
   </si>
   <si>
     <t>Popular demand for that new souvenir</t>
-  </si>
-  <si>
-    <t>Retail Manager wants to add a new souvenir. First the retail manager needs to click the Add souvenir button. After that the system directs the user to the Add Souvenir Page. The user needs to select a picture for the souvenir, then identify the name and set an appropriate description and price. After that the user needs to click the add button. The system will validate the input (such as price &gt; 0 and if the picture is valid and if the item name is unique and name &amp; description is not null). If the validation passes the system will create the souvenir object and insert it into the database.</t>
   </si>
   <si>
     <t>Retail Manager</t>
@@ -301,9 +292,6 @@
     <t>1. Retail Manager clicks the add new souvenir button</t>
   </si>
   <si>
-    <t>1.1 Redirects the user to the Add New Souvenir Page</t>
-  </si>
-  <si>
     <t>2. Retail Manager fills in the form</t>
   </si>
   <si>
@@ -392,9 +380,6 @@
 3. F&amp;B Supervisor needs to identify the name and price that makes sense (price &gt; 0)</t>
   </si>
   <si>
-    <t>2.1 The specified restaurant does not exist</t>
-  </si>
-  <si>
     <t>3.3 The F&amp;B Supervisor enters a negative price</t>
   </si>
   <si>
@@ -414,12 +399,6 @@
 3. The log to be updated must exist in the database.</t>
   </si>
   <si>
-    <t>1.2 Validates that the log id exists</t>
-  </si>
-  <si>
-    <t>1.2 The log id does not exist</t>
-  </si>
-  <si>
     <t>View Lost and Found Items Log</t>
   </si>
   <si>
@@ -546,9 +525,6 @@
     <t>2.1 The system validates whether the customer has enough money</t>
   </si>
   <si>
-    <t>2.3 The system redirects the customer back to the View All Souvenirs Page</t>
-  </si>
-  <si>
     <t>2.2 The system deducts the customer's money according to the purchase and saves it to the database</t>
   </si>
   <si>
@@ -586,9 +562,6 @@
   </si>
   <si>
     <t>Login Customer</t>
-  </si>
-  <si>
-    <t>View All Souvenirs, Login Customer, Open Store</t>
   </si>
   <si>
     <t>Customer wants to make a purchase, hence the need for them to log in.</t>
@@ -636,9 +609,6 @@
   </si>
   <si>
     <t>2.1 The UID is not found, the system will display an error</t>
-  </si>
-  <si>
-    <t>Propose New Restaurants</t>
   </si>
   <si>
     <t>Retail Manager wants to propose a new store</t>
@@ -795,149 +765,18 @@
     <t>CEO wants to clear the proposal queue</t>
   </si>
   <si>
-    <t>F&amp;B Supervisor wants to propose a new restaurant</t>
-  </si>
-  <si>
-    <t>F&amp;B Supervisor finds a good opportunity in a new restaurant</t>
-  </si>
-  <si>
-    <t>Manage New Restaurant Proposals</t>
-  </si>
-  <si>
-    <t>1. F&amp;B Supervisor must be logged in
-2. Restaurant name must be unique
-3. F&amp;B Supervisor has the relevant information to fill in the form</t>
-  </si>
-  <si>
-    <t>1. The proposal will be saved to the database
-2. The F&amp;B Manager will be redirected to the View All Restaurants Page</t>
-  </si>
-  <si>
     <t>Manage New Store Proposals, View All Stores</t>
   </si>
   <si>
-    <t>Manage New Restaurant Proposals, View All Restaurant Data</t>
-  </si>
-  <si>
-    <t>1.1 Creates a modal prompting the retail manager to fill in the fields</t>
-  </si>
-  <si>
-    <t>1.1 Creates a modal prompting the F&amp;B Supervisor to fill in the fields</t>
-  </si>
-  <si>
-    <t>1. F&amp;B Supervisor clicks the propose new restaurant button</t>
-  </si>
-  <si>
-    <t>2. F&amp;B Supervisor fills the fields and clicks "propose" button</t>
-  </si>
-  <si>
-    <t>View All Restaurant Data</t>
-  </si>
-  <si>
-    <t>After the F&amp;B Supervisor proposes the new restaurant, they'll get redirected to the View All Restaurants Page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F&amp;B Supervisor </t>
-  </si>
-  <si>
-    <t>F&amp;B Supervisor wants to view all restaurant data</t>
-  </si>
-  <si>
-    <t>F&amp;B Supervisor wants to view delete restaurant</t>
-  </si>
-  <si>
-    <t>F&amp;B Supervisor gets to see all stores here. They can choose further actions from this page (Propose New Restaurant/Remove Restaurant)</t>
-  </si>
-  <si>
-    <t>Propose New Restaurant, Delete Restaurant</t>
-  </si>
-  <si>
-    <t>1. The F&amp;B Supervisor must be logged in.
-2. The system fetches all restaurant data from the database. The database connection must be set.</t>
-  </si>
-  <si>
-    <t>1.1 System fetches the restaurant data from the database</t>
-  </si>
-  <si>
-    <t>1.2 System displays the restaurants to the F&amp;B Supervisor</t>
-  </si>
-  <si>
-    <t>CEO and CFO needs to both agree on the creation of a new restaurant.</t>
-  </si>
-  <si>
-    <t>CEO and CFO receives the proposal from the F&amp;B Supervisor.</t>
-  </si>
-  <si>
-    <t>After analyzing the financial reports by the CFO, it was concluded that VorteKia's annual income has been increasing as its popularity rises. With this, expansion comes into mind. The F&amp;B supervisor decides to expand and propose a new restaurant. In order to do this, the manager needs to navigate to the Propose New Restautant Page. There will be multiple fields to be filled, this includes: restaurant name, location photo, opening and closing times, and cuisine type. The system will validate the input such that all the fields are filled. If the validation passes the proposal will be saved into the database.</t>
-  </si>
-  <si>
-    <t>2.2 The system validates the fields should not be empty</t>
-  </si>
-  <si>
     <t>2.4 The system creates the proposal and saves it into the database</t>
   </si>
   <si>
-    <t>2.5 The system redirects the user to the View All Restaurants Page</t>
-  </si>
-  <si>
-    <t>2.2 Some fields are empty</t>
-  </si>
-  <si>
     <t>2.4 Database connection is lost</t>
   </si>
   <si>
-    <t>1. System Displays all restaurants to the F&amp;B Supervisor</t>
-  </si>
-  <si>
-    <t>1. F&amp;B enters the View All Restaurants Page</t>
-  </si>
-  <si>
-    <t>CEO and CFO wants to clear the proposal queue</t>
-  </si>
-  <si>
-    <t>F&amp;B Supervisor wants to propose a new restaurant. The CEO and CFO considers whether the proposal is any good. Based on this they can either approve or decline the new store proposal. The proposal requires both the CEO and CFO's acceptance for the restaurant to be created. If both accepts, the restaurant will be created and saved in to the database.</t>
-  </si>
-  <si>
-    <t>CEO, CFO</t>
-  </si>
-  <si>
-    <t>Propose New Restaurant</t>
-  </si>
-  <si>
-    <t>1. F&amp;B Supervisor: Writes the proposal
-2. CEO: In charge to accept/decline the proposal
-3. CFO: In charge to acccept/decline the proposal</t>
-  </si>
-  <si>
-    <t>1. CEO and CFO must be logged in
-2. CEO and CFO must make sure that the restaurant is well thought and analyze its potential before accepting/declining</t>
-  </si>
-  <si>
-    <t>1. The new restaurant will be created
-2. The new restaurant will be saved to the database</t>
-  </si>
-  <si>
     <t>1. CEO enters the Manage Store Proposals Page</t>
   </si>
   <si>
-    <t>1.1 System fetches the new restaurant proposals from the database</t>
-  </si>
-  <si>
-    <t>2. CEO and CFO clicks the "accept" button on a proposal</t>
-  </si>
-  <si>
-    <t>1. CEO and CFO enters the View New Restaurant Proposals Page</t>
-  </si>
-  <si>
-    <t>1.2 System displays the proposals to the CEO and CFO.</t>
-  </si>
-  <si>
-    <t>2.1 The system geneates the new restaurant and saves it into the database</t>
-  </si>
-  <si>
-    <t>1.2 If there are no proposals the system will show a No New Restaurant Proposals screen</t>
-  </si>
-  <si>
     <t>Propose New Ride</t>
   </si>
   <si>
@@ -951,9 +790,6 @@
   </si>
   <si>
     <t>Ride Manager finds a good opportunity in the new ride</t>
-  </si>
-  <si>
-    <t>Manage New ride Proposals</t>
   </si>
   <si>
     <t>1. The proposal will be saved to the database
@@ -1022,12 +858,6 @@
 4. COO: Will try to figure out how to setup the ride, the staff for the ride, and how it'll operate. Will also be the actor that accepts/declines the proposal.</t>
   </si>
   <si>
-    <t>1. F&amp;B Supervisor: Writes the proposal
-2. CEO: In charge to accept/decline the proposal
-3. CFO: Will try to calculate the budget needed for the new restaurant. Will be the second actor that also accepts/declines the proposal.
-4. COO: Will try to figure out the operation aspect of the new restaurant</t>
-  </si>
-  <si>
     <t>1.1 Creates a modal prompting the Ride manager to fill in the fields</t>
   </si>
   <si>
@@ -1040,18 +870,6 @@
     <t>2.3 The design prototype image is corrupt</t>
   </si>
   <si>
-    <t>2.3 The system validates the location photo must not be corrupt</t>
-  </si>
-  <si>
-    <t>2.1 The system validates the restaurant name must be unique</t>
-  </si>
-  <si>
-    <t>2.1 The restaurant name is not unique</t>
-  </si>
-  <si>
-    <t>2.3 The photo is corrupted and can't be displayed</t>
-  </si>
-  <si>
     <t>Propose New Rides, Delete Rides</t>
   </si>
   <si>
@@ -1068,9 +886,6 @@
   </si>
   <si>
     <t>COO</t>
-  </si>
-  <si>
-    <t>Propose New Ride Ideas</t>
   </si>
   <si>
     <t>1. Ride Manager: Writes the proposal
@@ -1096,7 +911,100 @@
     <t>1.1 System fetches the Ride proposals from the database</t>
   </si>
   <si>
-    <t>2.1 The system geneates the Ride and saves it into the database</t>
+    <t>2.1 Shows the new menu item form</t>
+  </si>
+  <si>
+    <t>1.2 Loads in the form with the current log data</t>
+  </si>
+  <si>
+    <t>Exeption Conditions:</t>
+  </si>
+  <si>
+    <t>2.3 The system saves the transaction to the database</t>
+  </si>
+  <si>
+    <t>2.3 The database connection is severed</t>
+  </si>
+  <si>
+    <t>2.4 The system redirects the customer back to the View All Souvenirs Page with a success message</t>
+  </si>
+  <si>
+    <t>1.1 Shows a modal prompting the retail manager to fill in the fields</t>
+  </si>
+  <si>
+    <t>Propose Ride Deletion</t>
+  </si>
+  <si>
+    <t>Ride Manager wants to propose a ride deletion</t>
+  </si>
+  <si>
+    <t>The ride isn't very well reviewed by customers</t>
+  </si>
+  <si>
+    <t>Ride Manager finds that the ride isn’t very popular</t>
+  </si>
+  <si>
+    <t>Manage Ride Proposals</t>
+  </si>
+  <si>
+    <t>1. Ride Manager: Writes the proposal
+2. CEO: Will analyze why the ride isn't doing very well
+3. CFO: Will try to calculate the losses
+4. COO: Will try to figure out how to make the ride more popular (by doing events and other activities)</t>
+  </si>
+  <si>
+    <t>1. Ride Manager clicks the propose ride deletion button</t>
+  </si>
+  <si>
+    <t>2.2 The system creates the proposal and saves it into the database</t>
+  </si>
+  <si>
+    <t>2.3 The system redirects the user to the View All rides Page</t>
+  </si>
+  <si>
+    <t>After the Ride manager proposes the ride deletion, they'll get redirected here</t>
+  </si>
+  <si>
+    <t>1. COO must be logged in
+2. COO must make sure that the proposal is well thought and beneficial before accepting/declining</t>
+  </si>
+  <si>
+    <t>COO chooses to accept or decline the Ride Deletion proposal</t>
+  </si>
+  <si>
+    <t>Ride Manager wants to propose a ride deletion. The COO considers whether the proposal is any good. Based on this they can either approve or decline the proposal. If the COO accepts, the ride will be deleted and the database will be saved.</t>
+  </si>
+  <si>
+    <t>Propose New Ride, Propose Ride Deletion</t>
+  </si>
+  <si>
+    <t>1. Ride Manager: Writes the proposal
+2. COO: In charge of analyzing the reason for Ride Deletion and accept/decline the proposal</t>
+  </si>
+  <si>
+    <t>2.1 The system deletes the Ride and saves it into the database</t>
+  </si>
+  <si>
+    <t>1. The ride will be deleted
+2. Database will be saved</t>
+  </si>
+  <si>
+    <t>2.1 The system generates the Ride and saves it into the database</t>
+  </si>
+  <si>
+    <t>Upon looking at sales report, the Ride manager noticed that the ride's popularity has been going down consistently. This is with multiple attempts to restore its hype. So unfortunately, the Ride Manager would need to delete it to recover from loss. Upon clicking the Propose Delete Button, there will be multiple fields to be filled, this includes: Ride ID and reason. The system will validate the input such that all the fields are filled. If the validation passes the proposal will be saved into the database.</t>
+  </si>
+  <si>
+    <t>1.1 Redirects the user to the Add New Souvenir Modal</t>
+  </si>
+  <si>
+    <t>Retail Manager wants to add a new souvenir. First the retail manager needs to click the Add souvenir button. After that the system displays the user to the Add Souvenir Modal. The user needs to select a picture for the souvenir, then identify the name and set an appropriate description and price. After that the user needs to click the add button. The system will validate the input (such as price &gt; 0 and if the picture is valid and if the item name is unique and name &amp; description is not null). If the validation passes the system will create the souvenir object and insert it into the database.</t>
+  </si>
+  <si>
+    <t>View All Souvenirs, Login Customer</t>
+  </si>
+  <si>
+    <t>2.1 The system validates the rideId must be valid</t>
   </si>
 </sst>
 </file>
@@ -1312,7 +1220,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1444,6 +1352,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1453,18 +1370,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1558,7 +1463,24 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1873,7 +1795,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A3915B7-9862-624A-8796-A82526CFDDED}">
-  <dimension ref="B2:D44"/>
+  <dimension ref="B2:D43"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="18.1640625" bestFit="1" customWidth="1"/>
@@ -1904,28 +1826,28 @@
         <v>2</v>
       </c>
       <c r="C4" s="46" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D4" s="47"/>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B5" s="49"/>
-      <c r="C5" s="54" t="s">
-        <v>106</v>
-      </c>
-      <c r="D5" s="55"/>
+      <c r="C5" s="52" t="s">
+        <v>102</v>
+      </c>
+      <c r="D5" s="53"/>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B6" s="39"/>
       <c r="C6" s="3"/>
       <c r="D6" s="4"/>
     </row>
-    <row r="7" spans="2:4" ht="95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:4" ht="84" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C7" s="44" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D7" s="45"/>
     </row>
@@ -1942,7 +1864,7 @@
         <v>5</v>
       </c>
       <c r="C9" s="46" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="D9" s="47"/>
     </row>
@@ -1960,7 +1882,7 @@
         <v>7</v>
       </c>
       <c r="C11" s="44" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D11" s="45"/>
     </row>
@@ -1999,257 +1921,249 @@
         <v>20</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>23</v>
+        <v>271</v>
       </c>
     </row>
     <row r="16" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="37"/>
-      <c r="C16" s="51" t="s">
+      <c r="C16" s="54" t="s">
         <v>22</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B17" s="37"/>
-      <c r="C17" s="52"/>
+      <c r="C17" s="55"/>
       <c r="D17" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B18" s="37"/>
-      <c r="C18" s="52"/>
+      <c r="C18" s="55"/>
       <c r="D18" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" spans="2:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="37"/>
-      <c r="C19" s="52"/>
+      <c r="C19" s="55"/>
       <c r="D19" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="2:4" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="37"/>
-      <c r="C20" s="52"/>
+      <c r="C20" s="55"/>
       <c r="D20" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B21" s="37"/>
-      <c r="C21" s="53"/>
+      <c r="C21" s="56"/>
       <c r="D21" s="7" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B22" s="36" t="s">
+      <c r="B22" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="C22" s="56" t="s">
-        <v>109</v>
-      </c>
-      <c r="D22" s="47"/>
+      <c r="C22" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B23" s="37"/>
-      <c r="C23" t="s">
+      <c r="C23" s="28" t="s">
         <v>29</v>
       </c>
+      <c r="D23" s="2"/>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B24" s="37"/>
       <c r="C24" s="28" t="s">
-        <v>30</v>
+        <v>105</v>
       </c>
       <c r="D24" s="2"/>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B25" s="37"/>
-      <c r="C25" s="28" t="s">
-        <v>110</v>
-      </c>
-      <c r="D25" s="2"/>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B26" s="57"/>
-      <c r="C26" s="29" t="s">
-        <v>111</v>
-      </c>
-      <c r="D26" s="9"/>
+      <c r="B25" s="51"/>
+      <c r="C25" s="29" t="s">
+        <v>106</v>
+      </c>
+      <c r="D25" s="9"/>
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B28" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C28" s="46" t="s">
+        <v>112</v>
+      </c>
+      <c r="D28" s="47"/>
     </row>
     <row r="29" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B29" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C29" s="46" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="D29" s="47"/>
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B30" s="1" t="s">
-        <v>1</v>
+      <c r="B30" s="38" t="s">
+        <v>2</v>
       </c>
       <c r="C30" s="46" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="D30" s="47"/>
     </row>
     <row r="31" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B31" s="38" t="s">
-        <v>2</v>
-      </c>
-      <c r="C31" s="46" t="s">
-        <v>118</v>
+      <c r="B31" s="49"/>
+      <c r="C31" s="50" t="s">
+        <v>14</v>
       </c>
       <c r="D31" s="47"/>
     </row>
     <row r="32" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B32" s="49"/>
+      <c r="B32" s="39"/>
       <c r="C32" s="50" t="s">
         <v>14</v>
       </c>
       <c r="D32" s="47"/>
     </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B33" s="39"/>
-      <c r="C33" s="50" t="s">
-        <v>14</v>
-      </c>
-      <c r="D33" s="47"/>
-    </row>
-    <row r="34" spans="2:4" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="5" t="s">
+    <row r="33" spans="2:4" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B33" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C34" s="44" t="s">
-        <v>123</v>
-      </c>
-      <c r="D34" s="45"/>
+      <c r="C33" s="44" t="s">
+        <v>116</v>
+      </c>
+      <c r="D33" s="45"/>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B34" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C34" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B35" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C35" t="s">
-        <v>15</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="C35" s="46" t="s">
+        <v>114</v>
+      </c>
+      <c r="D35" s="47"/>
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B36" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C36" s="46" t="s">
-        <v>121</v>
+        <v>6</v>
+      </c>
+      <c r="C36" s="48" t="s">
+        <v>14</v>
       </c>
       <c r="D36" s="47"/>
     </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B37" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="48" t="s">
-        <v>14</v>
-      </c>
-      <c r="D37" s="47"/>
-    </row>
-    <row r="38" spans="2:4" ht="34" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B38" s="10" t="s">
+    <row r="37" spans="2:4" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B37" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C38" s="44" t="s">
-        <v>91</v>
-      </c>
-      <c r="D38" s="45"/>
-    </row>
-    <row r="39" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B39" s="1" t="s">
+      <c r="C37" s="44" t="s">
+        <v>87</v>
+      </c>
+      <c r="D37" s="45"/>
+    </row>
+    <row r="38" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B38" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C39" s="48" t="s">
-        <v>90</v>
-      </c>
-      <c r="D39" s="47"/>
+      <c r="C38" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="D38" s="47"/>
+    </row>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B39" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="40" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B40" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>11</v>
+      <c r="B40" s="37"/>
+      <c r="C40" s="42" t="s">
+        <v>88</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B41" s="37"/>
-      <c r="C41" s="42" t="s">
-        <v>92</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B42" s="37"/>
-      <c r="C42" s="43"/>
-      <c r="D42" s="8" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="43" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B43" s="38" t="s">
+      <c r="C41" s="43"/>
+      <c r="D41" s="8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B42" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="C43" s="40" t="s">
-        <v>168</v>
-      </c>
-      <c r="D43" s="41"/>
-    </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B44" s="39"/>
-      <c r="C44" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="D44" s="8"/>
+      <c r="C42" s="40" t="s">
+        <v>160</v>
+      </c>
+      <c r="D42" s="41"/>
+    </row>
+    <row r="43" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B43" s="39"/>
+      <c r="C43" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="D43" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="28">
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C16:C21"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="B30:B32"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C32:D32"/>
     <mergeCell ref="B13:B21"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="B22:B26"/>
+    <mergeCell ref="B22:B25"/>
     <mergeCell ref="B4:B6"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C16:C21"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="B31:B33"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="B39:B41"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C40:C41"/>
     <mergeCell ref="C33:D33"/>
-    <mergeCell ref="B40:B42"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="C37:D37"/>
     <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C39:D39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2274,38 +2188,38 @@
       <c r="B2" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="62" t="s">
-        <v>31</v>
-      </c>
-      <c r="D2" s="63"/>
+      <c r="C2" s="61" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="62"/>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="62" t="s">
+      <c r="C3" s="61" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="62"/>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B4" s="68" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="61" t="s">
         <v>32</v>
       </c>
-      <c r="D3" s="63"/>
-    </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B4" s="69" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="62" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="63"/>
+      <c r="D4" s="62"/>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B5" s="70"/>
-      <c r="C5" s="72" t="s">
-        <v>112</v>
-      </c>
-      <c r="D5" s="73"/>
+      <c r="B5" s="69"/>
+      <c r="C5" s="71" t="s">
+        <v>107</v>
+      </c>
+      <c r="D5" s="72"/>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B6" s="71"/>
+      <c r="B6" s="70"/>
       <c r="C6" s="14"/>
       <c r="D6" s="15"/>
     </row>
@@ -2313,17 +2227,17 @@
       <c r="B7" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="64" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" s="65"/>
+      <c r="C7" s="63" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="64"/>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B8" s="13" t="s">
         <v>4</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D8" s="11"/>
     </row>
@@ -2331,17 +2245,17 @@
       <c r="B9" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="62" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" s="63"/>
+      <c r="C9" s="61" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="62"/>
     </row>
     <row r="10" spans="2:4" ht="52" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="13" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="40" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D10" s="41"/>
     </row>
@@ -2349,22 +2263,22 @@
       <c r="B11" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="64" t="s">
-        <v>113</v>
-      </c>
-      <c r="D11" s="65"/>
+      <c r="C11" s="63" t="s">
+        <v>108</v>
+      </c>
+      <c r="D11" s="64"/>
     </row>
     <row r="12" spans="2:4" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="40" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D12" s="41"/>
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B13" s="58" t="s">
+      <c r="B13" s="57" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="21" t="s">
@@ -2375,127 +2289,127 @@
       </c>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B14" s="58"/>
+      <c r="B14" s="57"/>
       <c r="C14" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="23" t="s">
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B15" s="57"/>
+      <c r="C15" s="65" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B15" s="58"/>
-      <c r="C15" s="66" t="s">
+      <c r="D15" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="25" t="s">
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B16" s="57"/>
+      <c r="C16" s="66"/>
+      <c r="D16" s="25" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B17" s="57"/>
+      <c r="C17" s="66"/>
+      <c r="D17" s="25" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B16" s="58"/>
-      <c r="C16" s="67"/>
-      <c r="D16" s="25" t="s">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B18" s="57"/>
+      <c r="C18" s="66"/>
+      <c r="D18" s="25" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B19" s="57"/>
+      <c r="C19" s="66"/>
+      <c r="D19" s="23" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B20" s="57"/>
+      <c r="C20" s="66"/>
+      <c r="D20" s="23" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B21" s="57"/>
+      <c r="C21" s="66"/>
+      <c r="D21" s="23" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B22" s="57"/>
+      <c r="C22" s="66"/>
+      <c r="D22" s="23" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B23" s="57"/>
+      <c r="C23" s="67"/>
+      <c r="D23" s="23" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B24" s="58" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" s="26" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B17" s="58"/>
-      <c r="C17" s="67"/>
-      <c r="D17" s="25" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B18" s="58"/>
-      <c r="C18" s="67"/>
-      <c r="D18" s="25" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B19" s="58"/>
-      <c r="C19" s="67"/>
-      <c r="D19" s="23" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B20" s="58"/>
-      <c r="C20" s="67"/>
-      <c r="D20" s="23" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B21" s="58"/>
-      <c r="C21" s="67"/>
-      <c r="D21" s="23" t="s">
+      <c r="D24" s="23"/>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B25" s="59"/>
+      <c r="C25" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="D25" s="23"/>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B26" s="59"/>
+      <c r="C26" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="D26" s="23"/>
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B27" s="59"/>
+      <c r="C27" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="D27" s="23"/>
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B28" s="59"/>
+      <c r="C28" s="22" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B22" s="58"/>
-      <c r="C22" s="67"/>
-      <c r="D22" s="23" t="s">
+      <c r="D28" s="23"/>
+    </row>
+    <row r="29" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B29" s="59"/>
+      <c r="C29" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="D29" s="8"/>
+    </row>
+    <row r="30" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B30" s="60"/>
+      <c r="C30" s="22" t="s">
         <v>54</v>
-      </c>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B23" s="58"/>
-      <c r="C23" s="68"/>
-      <c r="D23" s="23" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="24" spans="2:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B24" s="59" t="s">
-        <v>12</v>
-      </c>
-      <c r="C24" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="D24" s="23"/>
-    </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B25" s="60"/>
-      <c r="C25" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="D25" s="23"/>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B26" s="60"/>
-      <c r="C26" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="D26" s="23"/>
-    </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B27" s="60"/>
-      <c r="C27" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="D27" s="23"/>
-    </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B28" s="60"/>
-      <c r="C28" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="D28" s="23"/>
-    </row>
-    <row r="29" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="60"/>
-      <c r="C29" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="D29" s="8"/>
-    </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B30" s="61"/>
-      <c r="C30" s="22" t="s">
-        <v>55</v>
       </c>
       <c r="D30" s="23"/>
     </row>
@@ -2504,7 +2418,7 @@
         <v>0</v>
       </c>
       <c r="C34" s="46" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="D34" s="47"/>
     </row>
@@ -2513,7 +2427,7 @@
         <v>1</v>
       </c>
       <c r="C35" s="46" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="D35" s="47"/>
     </row>
@@ -2522,14 +2436,14 @@
         <v>2</v>
       </c>
       <c r="C36" s="46" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D36" s="47"/>
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B37" s="49"/>
       <c r="C37" s="46" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D37" s="47"/>
     </row>
@@ -2543,7 +2457,7 @@
         <v>3</v>
       </c>
       <c r="C39" s="44" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D39" s="45"/>
     </row>
@@ -2552,7 +2466,7 @@
         <v>4</v>
       </c>
       <c r="C40" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.2">
@@ -2560,7 +2474,7 @@
         <v>5</v>
       </c>
       <c r="C41" s="46" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D41" s="47"/>
     </row>
@@ -2578,7 +2492,7 @@
         <v>7</v>
       </c>
       <c r="C43" s="44" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D43" s="45"/>
     </row>
@@ -2587,7 +2501,7 @@
         <v>8</v>
       </c>
       <c r="C44" s="48" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D44" s="47"/>
     </row>
@@ -2605,17 +2519,17 @@
     <row r="46" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B46" s="37"/>
       <c r="C46" s="42" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="47" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B47" s="37"/>
       <c r="C47" s="43"/>
       <c r="D47" s="8" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="48" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2623,14 +2537,14 @@
         <v>12</v>
       </c>
       <c r="C48" s="40" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="D48" s="41"/>
     </row>
     <row r="49" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B49" s="39"/>
       <c r="C49" s="8" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="D49" s="8"/>
     </row>
@@ -2671,7 +2585,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09700A29-6BF4-5D4E-B89B-6596CAD66037}">
-  <dimension ref="B1:D52"/>
+  <dimension ref="B1:D50"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="18.1640625" bestFit="1" customWidth="1"/>
@@ -2688,38 +2602,38 @@
       <c r="B2" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="62" t="s">
-        <v>56</v>
-      </c>
-      <c r="D2" s="63"/>
+      <c r="C2" s="61" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" s="62"/>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="62" t="s">
+      <c r="C3" s="61" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="62"/>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B4" s="68" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="61" t="s">
         <v>57</v>
       </c>
-      <c r="D3" s="63"/>
-    </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B4" s="69" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="62" t="s">
+      <c r="D4" s="62"/>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B5" s="69"/>
+      <c r="C5" s="71" t="s">
         <v>58</v>
       </c>
-      <c r="D4" s="63"/>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B5" s="70"/>
-      <c r="C5" s="72" t="s">
-        <v>59</v>
-      </c>
-      <c r="D5" s="73"/>
+      <c r="D5" s="72"/>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B6" s="71"/>
+      <c r="B6" s="70"/>
       <c r="C6" s="14"/>
       <c r="D6" s="15"/>
     </row>
@@ -2727,17 +2641,17 @@
       <c r="B7" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="64" t="s">
-        <v>60</v>
-      </c>
-      <c r="D7" s="65"/>
+      <c r="C7" s="63" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" s="64"/>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B8" s="13" t="s">
         <v>4</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D8" s="11"/>
     </row>
@@ -2745,17 +2659,17 @@
       <c r="B9" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="62" t="s">
-        <v>70</v>
-      </c>
-      <c r="D9" s="63"/>
+      <c r="C9" s="61" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" s="62"/>
     </row>
     <row r="10" spans="2:4" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="13" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="40" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D10" s="41"/>
     </row>
@@ -2763,22 +2677,22 @@
       <c r="B11" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="64" t="s">
-        <v>114</v>
-      </c>
-      <c r="D11" s="65"/>
+      <c r="C11" s="63" t="s">
+        <v>109</v>
+      </c>
+      <c r="D11" s="64"/>
     </row>
     <row r="12" spans="2:4" ht="49" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="40" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D12" s="41"/>
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B13" s="58" t="s">
+      <c r="B13" s="57" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="21" t="s">
@@ -2789,285 +2703,271 @@
       </c>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B14" s="58"/>
-      <c r="C14" s="74" t="s">
+      <c r="B14" s="57"/>
+      <c r="C14" s="73" t="s">
+        <v>63</v>
+      </c>
+      <c r="D14" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="D14" s="23" t="s">
-        <v>65</v>
-      </c>
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B15" s="58"/>
-      <c r="C15" s="74"/>
+      <c r="B15" s="57"/>
+      <c r="C15" s="73"/>
       <c r="D15" s="8" t="s">
-        <v>115</v>
+        <v>272</v>
       </c>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B16" s="58"/>
-      <c r="C16" s="74"/>
-      <c r="D16" s="8" t="s">
-        <v>69</v>
+      <c r="B16" s="57"/>
+      <c r="C16" s="73" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="25" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B17" s="58"/>
-      <c r="C17" s="74" t="s">
-        <v>40</v>
-      </c>
+      <c r="B17" s="57"/>
+      <c r="C17" s="73"/>
       <c r="D17" s="25" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B18" s="57"/>
+      <c r="C18" s="73"/>
+      <c r="D18" s="25" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B18" s="58"/>
-      <c r="C18" s="74"/>
-      <c r="D18" s="25" t="s">
-        <v>46</v>
-      </c>
-    </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B19" s="58"/>
-      <c r="C19" s="74"/>
+      <c r="B19" s="57"/>
+      <c r="C19" s="73"/>
       <c r="D19" s="25" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B20" s="58"/>
-      <c r="C20" s="74"/>
-      <c r="D20" s="25" t="s">
+      <c r="B20" s="57"/>
+      <c r="C20" s="73"/>
+      <c r="D20" s="23" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B21" s="58"/>
-      <c r="C21" s="74"/>
+      <c r="B21" s="57"/>
+      <c r="C21" s="73"/>
       <c r="D21" s="23" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B22" s="58"/>
-      <c r="C22" s="74"/>
+      <c r="B22" s="57"/>
+      <c r="C22" s="73"/>
       <c r="D22" s="23" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B23" s="58"/>
-      <c r="C23" s="74"/>
+      <c r="B23" s="57"/>
+      <c r="C23" s="73"/>
       <c r="D23" s="23" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B24" s="58"/>
-      <c r="C24" s="74"/>
+      <c r="B24" s="57"/>
+      <c r="C24" s="73"/>
       <c r="D24" s="23" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B25" s="57" t="s">
+        <v>273</v>
+      </c>
+      <c r="C25" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="D25" s="23"/>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B26" s="57"/>
+      <c r="C26" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="D26" s="23"/>
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B27" s="57"/>
+      <c r="C27" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="D27" s="8"/>
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B28" s="57"/>
+      <c r="C28" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="D28" s="23"/>
+    </row>
+    <row r="29" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B29" s="57"/>
+      <c r="C29" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="D29" s="8"/>
+    </row>
+    <row r="30" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B30" s="57"/>
+      <c r="C30" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="D30" s="23"/>
+    </row>
+    <row r="31" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B31" s="57"/>
+      <c r="C31" s="22" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B25" s="58"/>
-      <c r="C25" s="74"/>
-      <c r="D25" s="23" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B26" s="58" t="s">
-        <v>12</v>
-      </c>
-      <c r="C26" t="s">
-        <v>116</v>
-      </c>
-      <c r="D26" s="23"/>
-    </row>
-    <row r="27" spans="2:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B27" s="58"/>
-      <c r="C27" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="D27" s="23"/>
-    </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B28" s="58"/>
-      <c r="C28" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="D28" s="23"/>
-    </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B29" s="58"/>
-      <c r="C29" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="D29" s="8"/>
-    </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B30" s="58"/>
-      <c r="C30" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="D30" s="23"/>
-    </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B31" s="58"/>
-      <c r="C31" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="D31" s="8"/>
-    </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B32" s="58"/>
-      <c r="C32" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="D32" s="23"/>
-    </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B33" s="58"/>
-      <c r="C33" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="D33" s="23"/>
+      <c r="D31" s="23"/>
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B35" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C35" s="46" t="s">
+        <v>110</v>
+      </c>
+      <c r="D35" s="47"/>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B36" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C36" s="46" t="s">
+        <v>122</v>
+      </c>
+      <c r="D36" s="47"/>
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B37" s="1" t="s">
-        <v>0</v>
+      <c r="B37" s="38" t="s">
+        <v>2</v>
       </c>
       <c r="C37" s="46" t="s">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="D37" s="47"/>
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B38" s="1" t="s">
-        <v>1</v>
-      </c>
+      <c r="B38" s="49"/>
       <c r="C38" s="46" t="s">
-        <v>129</v>
+        <v>92</v>
       </c>
       <c r="D38" s="47"/>
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B39" s="38" t="s">
-        <v>2</v>
-      </c>
-      <c r="C39" s="46" t="s">
-        <v>95</v>
-      </c>
+      <c r="B39" s="39"/>
+      <c r="C39" s="46"/>
       <c r="D39" s="47"/>
     </row>
     <row r="40" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B40" s="49"/>
-      <c r="C40" s="46" t="s">
-        <v>96</v>
-      </c>
-      <c r="D40" s="47"/>
+      <c r="B40" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C40" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="D40" s="45"/>
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B41" s="39"/>
-      <c r="C41" s="46"/>
-      <c r="D41" s="47"/>
+      <c r="B41" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C41" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="42" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B42" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C42" s="44" t="s">
-        <v>97</v>
-      </c>
-      <c r="D42" s="45"/>
+      <c r="B42" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C42" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="D42" s="47"/>
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B43" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C43" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B44" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C44" s="46" t="s">
-        <v>98</v>
-      </c>
-      <c r="D44" s="47"/>
+        <v>6</v>
+      </c>
+      <c r="C43" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="D43" s="47"/>
+    </row>
+    <row r="44" spans="2:4" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B44" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="44" t="s">
+        <v>95</v>
+      </c>
+      <c r="D44" s="45"/>
     </row>
     <row r="45" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B45" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C45" s="48" t="s">
-        <v>14</v>
+        <v>96</v>
       </c>
       <c r="D45" s="47"/>
     </row>
-    <row r="46" spans="2:4" ht="37" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B46" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46" s="44" t="s">
+    <row r="46" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B46" s="36" t="s">
+        <v>9</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B47" s="37"/>
+      <c r="C47" s="42" t="s">
+        <v>97</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B48" s="37"/>
+      <c r="C48" s="43"/>
+      <c r="D48" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="D46" s="45"/>
-    </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B47" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C47" s="48" t="s">
+    </row>
+    <row r="49" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B49" s="38" t="s">
+        <v>12</v>
+      </c>
+      <c r="C49" s="40" t="s">
+        <v>160</v>
+      </c>
+      <c r="D49" s="41"/>
+    </row>
+    <row r="50" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B50" s="39"/>
+      <c r="C50" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="D47" s="47"/>
-    </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B48" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B49" s="37"/>
-      <c r="C49" s="42" t="s">
-        <v>101</v>
-      </c>
-      <c r="D49" s="7" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B50" s="37"/>
-      <c r="C50" s="43"/>
-      <c r="D50" s="8" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="51" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B51" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="C51" s="40" t="s">
-        <v>168</v>
-      </c>
-      <c r="D51" s="41"/>
-    </row>
-    <row r="52" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B52" s="39"/>
-      <c r="C52" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="D52" s="8"/>
+      <c r="D50" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="29">
@@ -3077,29 +2977,29 @@
     <mergeCell ref="B4:B6"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="C5:D5"/>
-    <mergeCell ref="B13:B25"/>
-    <mergeCell ref="C14:C16"/>
-    <mergeCell ref="C17:C25"/>
-    <mergeCell ref="B26:B33"/>
+    <mergeCell ref="B13:B24"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="C16:C24"/>
+    <mergeCell ref="B25:B31"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="B37:B39"/>
     <mergeCell ref="C37:D37"/>
     <mergeCell ref="C38:D38"/>
-    <mergeCell ref="B39:B41"/>
     <mergeCell ref="C39:D39"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="C49:D49"/>
     <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="B51:B52"/>
-    <mergeCell ref="C51:D51"/>
     <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C43:D43"/>
     <mergeCell ref="C44:D44"/>
     <mergeCell ref="C45:D45"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="C49:C50"/>
+    <mergeCell ref="B46:B48"/>
+    <mergeCell ref="C47:C48"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3124,38 +3024,38 @@
       <c r="B2" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="62" t="s">
-        <v>71</v>
-      </c>
-      <c r="D2" s="63"/>
+      <c r="C2" s="61" t="s">
+        <v>69</v>
+      </c>
+      <c r="D2" s="62"/>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="62" t="s">
-        <v>73</v>
-      </c>
-      <c r="D3" s="63"/>
+      <c r="C3" s="61" t="s">
+        <v>71</v>
+      </c>
+      <c r="D3" s="62"/>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B4" s="69" t="s">
+      <c r="B4" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="62" t="s">
+      <c r="C4" s="61" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" s="62"/>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B5" s="69"/>
+      <c r="C5" s="71" t="s">
         <v>72</v>
       </c>
-      <c r="D4" s="63"/>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B5" s="70"/>
-      <c r="C5" s="72" t="s">
-        <v>74</v>
-      </c>
-      <c r="D5" s="73"/>
+      <c r="D5" s="72"/>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B6" s="71"/>
+      <c r="B6" s="70"/>
       <c r="C6" s="14"/>
       <c r="D6" s="15"/>
     </row>
@@ -3164,7 +3064,7 @@
         <v>3</v>
       </c>
       <c r="C7" s="44" t="s">
-        <v>75</v>
+        <v>298</v>
       </c>
       <c r="D7" s="45"/>
     </row>
@@ -3173,7 +3073,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D8" s="11"/>
     </row>
@@ -3181,17 +3081,17 @@
       <c r="B9" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="75" t="s">
-        <v>132</v>
-      </c>
-      <c r="D9" s="63"/>
+      <c r="C9" s="74" t="s">
+        <v>125</v>
+      </c>
+      <c r="D9" s="62"/>
     </row>
     <row r="10" spans="2:4" ht="49" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="13" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="40" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D10" s="41"/>
     </row>
@@ -3199,22 +3099,22 @@
       <c r="B11" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="64" t="s">
-        <v>78</v>
-      </c>
-      <c r="D11" s="65"/>
+      <c r="C11" s="63" t="s">
+        <v>75</v>
+      </c>
+      <c r="D11" s="64"/>
     </row>
     <row r="12" spans="2:4" ht="60" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="40" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D12" s="41"/>
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B13" s="58" t="s">
+      <c r="B13" s="57" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="21" t="s">
@@ -3225,99 +3125,99 @@
       </c>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B14" s="58"/>
+      <c r="B14" s="57"/>
       <c r="C14" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="D14" s="23" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B15" s="57"/>
+      <c r="C15" s="73" t="s">
+        <v>77</v>
+      </c>
+      <c r="D15" s="25" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B16" s="57"/>
+      <c r="C16" s="73"/>
+      <c r="D16" s="25" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B17" s="57"/>
+      <c r="C17" s="73"/>
+      <c r="D17" s="25" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B18" s="57"/>
+      <c r="C18" s="73"/>
+      <c r="D18" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="D14" s="23" t="s">
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B19" s="57"/>
+      <c r="C19" s="73"/>
+      <c r="D19" s="23" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B15" s="58"/>
-      <c r="C15" s="74" t="s">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B20" s="57"/>
+      <c r="C20" s="73"/>
+      <c r="D20" s="23" t="s">
         <v>81</v>
       </c>
-      <c r="D15" s="25" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B16" s="58"/>
-      <c r="C16" s="74"/>
-      <c r="D16" s="25" t="s">
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B21" s="57"/>
+      <c r="C21" s="73"/>
+      <c r="D21" s="23" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="B22" s="57" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="26" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B17" s="58"/>
-      <c r="C17" s="74"/>
-      <c r="D17" s="25" t="s">
+      <c r="D22" s="8"/>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B23" s="57"/>
+      <c r="C23" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="D23" s="23"/>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B24" s="57"/>
+      <c r="C24" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="D24" s="8"/>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B25" s="57"/>
+      <c r="C25" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="D25" s="23"/>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B26" s="57"/>
+      <c r="C26" s="22" t="s">
         <v>82</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B18" s="58"/>
-      <c r="C18" s="74"/>
-      <c r="D18" s="25" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B19" s="58"/>
-      <c r="C19" s="74"/>
-      <c r="D19" s="23" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B20" s="58"/>
-      <c r="C20" s="74"/>
-      <c r="D20" s="23" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B21" s="58"/>
-      <c r="C21" s="74"/>
-      <c r="D21" s="23" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="22" spans="2:4" ht="17" x14ac:dyDescent="0.2">
-      <c r="B22" s="58" t="s">
-        <v>12</v>
-      </c>
-      <c r="C22" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="D22" s="8"/>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B23" s="58"/>
-      <c r="C23" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="D23" s="23"/>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B24" s="58"/>
-      <c r="C24" s="22" t="s">
-        <v>87</v>
-      </c>
-      <c r="D24" s="8"/>
-    </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B25" s="58"/>
-      <c r="C25" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="D25" s="23"/>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B26" s="58"/>
-      <c r="C26" s="22" t="s">
-        <v>86</v>
       </c>
       <c r="D26" s="23"/>
     </row>
@@ -3325,58 +3225,58 @@
       <c r="B30" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C30" s="62" t="s">
-        <v>132</v>
-      </c>
-      <c r="D30" s="63"/>
+      <c r="C30" s="61" t="s">
+        <v>125</v>
+      </c>
+      <c r="D30" s="62"/>
     </row>
     <row r="31" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B31" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C31" s="62" t="s">
-        <v>133</v>
-      </c>
-      <c r="D31" s="63"/>
+      <c r="C31" s="61" t="s">
+        <v>126</v>
+      </c>
+      <c r="D31" s="62"/>
     </row>
     <row r="32" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B32" s="69" t="s">
+      <c r="B32" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="62" t="s">
-        <v>134</v>
-      </c>
-      <c r="D32" s="63"/>
+      <c r="C32" s="61" t="s">
+        <v>127</v>
+      </c>
+      <c r="D32" s="62"/>
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B33" s="70"/>
-      <c r="C33" s="62" t="s">
-        <v>135</v>
-      </c>
-      <c r="D33" s="63"/>
+      <c r="B33" s="69"/>
+      <c r="C33" s="61" t="s">
+        <v>128</v>
+      </c>
+      <c r="D33" s="62"/>
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B34" s="71"/>
-      <c r="C34" s="62" t="s">
-        <v>136</v>
-      </c>
-      <c r="D34" s="63"/>
+      <c r="B34" s="70"/>
+      <c r="C34" s="61" t="s">
+        <v>129</v>
+      </c>
+      <c r="D34" s="62"/>
     </row>
     <row r="35" spans="2:4" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B35" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="C35" s="64" t="s">
-        <v>137</v>
-      </c>
-      <c r="D35" s="65"/>
+      <c r="C35" s="63" t="s">
+        <v>130</v>
+      </c>
+      <c r="D35" s="64"/>
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B36" s="13" t="s">
         <v>4</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D36" s="11"/>
     </row>
@@ -3384,10 +3284,10 @@
       <c r="B37" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C37" s="62" t="s">
-        <v>163</v>
-      </c>
-      <c r="D37" s="63"/>
+      <c r="C37" s="61" t="s">
+        <v>155</v>
+      </c>
+      <c r="D37" s="62"/>
     </row>
     <row r="38" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B38" s="13" t="s">
@@ -3402,22 +3302,22 @@
       <c r="B39" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C39" s="64" t="s">
-        <v>138</v>
-      </c>
-      <c r="D39" s="65"/>
+      <c r="C39" s="63" t="s">
+        <v>131</v>
+      </c>
+      <c r="D39" s="64"/>
     </row>
     <row r="40" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B40" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C40" s="40" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="D40" s="41"/>
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B41" s="59" t="s">
+      <c r="B41" s="58" t="s">
         <v>9</v>
       </c>
       <c r="C41" s="18" t="s">
@@ -3428,34 +3328,34 @@
       </c>
     </row>
     <row r="42" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B42" s="60"/>
-      <c r="C42" s="66" t="s">
-        <v>140</v>
+      <c r="B42" s="59"/>
+      <c r="C42" s="65" t="s">
+        <v>133</v>
       </c>
       <c r="D42" s="20" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B43" s="61"/>
-      <c r="C43" s="68"/>
+      <c r="B43" s="60"/>
+      <c r="C43" s="67"/>
       <c r="D43" s="19" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
     </row>
     <row r="44" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B44" s="69" t="s">
+      <c r="B44" s="68" t="s">
         <v>12</v>
       </c>
       <c r="C44" s="40" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="D44" s="41"/>
     </row>
     <row r="45" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B45" s="71"/>
+      <c r="B45" s="70"/>
       <c r="C45" s="19" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="D45" s="19"/>
     </row>
@@ -3496,7 +3396,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{850C9DDC-922A-2147-A5BB-1C7F42653EAC}">
-  <dimension ref="B1:D71"/>
+  <dimension ref="B1:D73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="18.1640625" bestFit="1" customWidth="1"/>
@@ -3513,38 +3413,38 @@
       <c r="B2" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="62" t="s">
-        <v>144</v>
-      </c>
-      <c r="D2" s="63"/>
+      <c r="C2" s="61" t="s">
+        <v>137</v>
+      </c>
+      <c r="D2" s="62"/>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="62" t="s">
-        <v>145</v>
-      </c>
-      <c r="D3" s="63"/>
+      <c r="C3" s="61" t="s">
+        <v>138</v>
+      </c>
+      <c r="D3" s="62"/>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B4" s="69" t="s">
+      <c r="B4" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="62" t="s">
-        <v>146</v>
-      </c>
-      <c r="D4" s="63"/>
+      <c r="C4" s="61" t="s">
+        <v>139</v>
+      </c>
+      <c r="D4" s="62"/>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B5" s="70"/>
-      <c r="C5" s="72" t="s">
-        <v>147</v>
-      </c>
-      <c r="D5" s="73"/>
+      <c r="B5" s="69"/>
+      <c r="C5" s="71" t="s">
+        <v>140</v>
+      </c>
+      <c r="D5" s="72"/>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B6" s="71"/>
+      <c r="B6" s="70"/>
       <c r="C6" s="14"/>
       <c r="D6" s="15"/>
     </row>
@@ -3553,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C7" s="44" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="D7" s="45"/>
     </row>
@@ -3562,7 +3462,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="D8" s="11"/>
     </row>
@@ -3570,17 +3470,17 @@
       <c r="B9" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="75" t="s">
-        <v>171</v>
-      </c>
-      <c r="D9" s="63"/>
+      <c r="C9" s="74" t="s">
+        <v>299</v>
+      </c>
+      <c r="D9" s="62"/>
     </row>
     <row r="10" spans="2:4" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="13" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="40" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="D10" s="41"/>
     </row>
@@ -3588,22 +3488,22 @@
       <c r="B11" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="64" t="s">
-        <v>155</v>
-      </c>
-      <c r="D11" s="65"/>
+      <c r="C11" s="63" t="s">
+        <v>148</v>
+      </c>
+      <c r="D11" s="64"/>
     </row>
     <row r="12" spans="2:4" ht="35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="40" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="D12" s="41"/>
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B13" s="58" t="s">
+      <c r="B13" s="57" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="21" t="s">
@@ -3614,335 +3514,352 @@
       </c>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B14" s="58"/>
+      <c r="B14" s="57"/>
       <c r="C14" s="27" t="s">
+        <v>145</v>
+      </c>
+      <c r="D14" s="23" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B15" s="57"/>
+      <c r="C15" s="73" t="s">
+        <v>147</v>
+      </c>
+      <c r="D15" s="25" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B16" s="57"/>
+      <c r="C16" s="73"/>
+      <c r="D16" s="25" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B17" s="57"/>
+      <c r="C17" s="73"/>
+      <c r="D17" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B18" s="57"/>
+      <c r="C18" s="73"/>
+      <c r="D18" s="25" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B19" s="58" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="23"/>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B20" s="59"/>
+      <c r="C20" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="D20" s="23"/>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B21" s="60"/>
+      <c r="C21" s="22" t="s">
+        <v>275</v>
+      </c>
+      <c r="D21" s="8"/>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="C22" s="22" t="s">
         <v>152</v>
       </c>
-      <c r="D14" s="23" t="s">
+      <c r="D22" s="8"/>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B25" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C25" s="61" t="s">
+        <v>125</v>
+      </c>
+      <c r="D25" s="62"/>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B26" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C26" s="61" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B15" s="58"/>
-      <c r="C15" s="74" t="s">
+      <c r="D26" s="62"/>
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B27" s="68" t="s">
+        <v>2</v>
+      </c>
+      <c r="C27" s="61" t="s">
+        <v>127</v>
+      </c>
+      <c r="D27" s="62"/>
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B28" s="69"/>
+      <c r="C28" s="61" t="s">
+        <v>128</v>
+      </c>
+      <c r="D28" s="62"/>
+    </row>
+    <row r="29" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B29" s="70"/>
+      <c r="C29" s="61" t="s">
+        <v>137</v>
+      </c>
+      <c r="D29" s="62"/>
+    </row>
+    <row r="30" spans="2:4" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B30" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="C30" s="63" t="s">
         <v>154</v>
       </c>
-      <c r="D15" s="25" t="s">
+      <c r="D30" s="64"/>
+    </row>
+    <row r="31" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B31" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="D31" s="11"/>
+    </row>
+    <row r="32" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B32" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C32" s="61" t="s">
+        <v>155</v>
+      </c>
+      <c r="D32" s="62"/>
+    </row>
+    <row r="33" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B33" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="80" t="s">
+        <v>14</v>
+      </c>
+      <c r="D33" s="41"/>
+    </row>
+    <row r="34" spans="2:4" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B34" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="63" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B16" s="58"/>
-      <c r="C16" s="74"/>
-      <c r="D16" s="25" t="s">
+      <c r="D34" s="64"/>
+    </row>
+    <row r="35" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B35" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" s="40" t="s">
+        <v>157</v>
+      </c>
+      <c r="D35" s="41"/>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B36" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D36" s="18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B37" s="59"/>
+      <c r="C37" s="65" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B17" s="58"/>
-      <c r="C17" s="74"/>
-      <c r="D17" s="25" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B18" s="59" t="s">
+      <c r="D37" s="20" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B38" s="60"/>
+      <c r="C38" s="67"/>
+      <c r="D38" s="19" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B39" s="68" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="22" t="s">
+      <c r="C39" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="D18" s="23"/>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B19" s="61"/>
-      <c r="C19" s="22" t="s">
-        <v>159</v>
-      </c>
-      <c r="D19" s="23"/>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B23" s="12" t="s">
+      <c r="D39" s="41"/>
+    </row>
+    <row r="40" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B40" s="70"/>
+      <c r="C40" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="D40" s="19"/>
+    </row>
+    <row r="44" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B44" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C23" s="62" t="s">
-        <v>132</v>
-      </c>
-      <c r="D23" s="63"/>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B24" s="13" t="s">
+      <c r="C44" s="77" t="s">
+        <v>162</v>
+      </c>
+      <c r="D44" s="77"/>
+    </row>
+    <row r="45" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B45" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C24" s="62" t="s">
-        <v>161</v>
-      </c>
-      <c r="D24" s="63"/>
-    </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B25" s="69" t="s">
+      <c r="C45" s="77" t="s">
+        <v>163</v>
+      </c>
+      <c r="D45" s="77"/>
+    </row>
+    <row r="46" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B46" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="C25" s="62" t="s">
-        <v>134</v>
-      </c>
-      <c r="D25" s="63"/>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B26" s="70"/>
-      <c r="C26" s="62" t="s">
-        <v>135</v>
-      </c>
-      <c r="D26" s="63"/>
-    </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B27" s="71"/>
-      <c r="C27" s="62" t="s">
-        <v>144</v>
-      </c>
-      <c r="D27" s="63"/>
-    </row>
-    <row r="28" spans="2:4" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="16" t="s">
+      <c r="C46" s="77" t="s">
+        <v>164</v>
+      </c>
+      <c r="D46" s="77"/>
+    </row>
+    <row r="47" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B47" s="79"/>
+      <c r="C47" s="77" t="s">
+        <v>165</v>
+      </c>
+      <c r="D47" s="77"/>
+    </row>
+    <row r="48" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B48" s="79"/>
+      <c r="C48" s="77" t="s">
+        <v>166</v>
+      </c>
+      <c r="D48" s="77"/>
+    </row>
+    <row r="49" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B49" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="C28" s="64" t="s">
-        <v>162</v>
-      </c>
-      <c r="D28" s="65"/>
-    </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B29" s="13" t="s">
+      <c r="C49" s="76" t="s">
+        <v>167</v>
+      </c>
+      <c r="D49" s="76"/>
+    </row>
+    <row r="50" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B50" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C29" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="D29" s="11"/>
-    </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B30" s="13" t="s">
+      <c r="C50" s="25" t="s">
+        <v>142</v>
+      </c>
+      <c r="D50" s="25"/>
+    </row>
+    <row r="51" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B51" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C30" s="62" t="s">
-        <v>163</v>
-      </c>
-      <c r="D30" s="63"/>
-    </row>
-    <row r="31" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="13" t="s">
+      <c r="C51" s="77" t="s">
+        <v>168</v>
+      </c>
+      <c r="D51" s="77"/>
+    </row>
+    <row r="52" spans="2:4" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B52" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C31" s="81" t="s">
-        <v>14</v>
-      </c>
-      <c r="D31" s="41"/>
-    </row>
-    <row r="32" spans="2:4" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B32" s="17" t="s">
+      <c r="C52" s="78" t="s">
+        <v>169</v>
+      </c>
+      <c r="D52" s="75"/>
+    </row>
+    <row r="53" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B53" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="C32" s="64" t="s">
-        <v>164</v>
-      </c>
-      <c r="D32" s="65"/>
-    </row>
-    <row r="33" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B33" s="12" t="s">
+      <c r="C53" s="76" t="s">
+        <v>170</v>
+      </c>
+      <c r="D53" s="76"/>
+    </row>
+    <row r="54" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B54" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="C33" s="40" t="s">
-        <v>165</v>
-      </c>
-      <c r="D33" s="41"/>
-    </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B34" s="59" t="s">
+      <c r="C54" s="75" t="s">
+        <v>171</v>
+      </c>
+      <c r="D54" s="75"/>
+    </row>
+    <row r="55" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B55" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="C34" s="18" t="s">
+      <c r="C55" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="D34" s="18" t="s">
+      <c r="D55" s="21" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B35" s="60"/>
-      <c r="C35" s="66" t="s">
-        <v>166</v>
-      </c>
-      <c r="D35" s="20" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B36" s="61"/>
-      <c r="C36" s="68"/>
-      <c r="D36" s="19" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="37" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B37" s="69" t="s">
+    <row r="56" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B56" s="57"/>
+      <c r="C56" s="30" t="s">
+        <v>172</v>
+      </c>
+      <c r="D56" s="23" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="57" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B57" s="57"/>
+      <c r="C57" s="73" t="s">
+        <v>174</v>
+      </c>
+      <c r="D57" s="25" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="58" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B58" s="57"/>
+      <c r="C58" s="73"/>
+      <c r="D58" s="8" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="59" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B59" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="C37" s="40" t="s">
-        <v>168</v>
-      </c>
-      <c r="D37" s="41"/>
-    </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B38" s="71"/>
-      <c r="C38" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="D38" s="19"/>
-    </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B42" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C42" s="78" t="s">
-        <v>170</v>
-      </c>
-      <c r="D42" s="78"/>
-    </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B43" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C43" s="78" t="s">
-        <v>172</v>
-      </c>
-      <c r="D43" s="78"/>
-    </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B44" s="80" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="78" t="s">
-        <v>173</v>
-      </c>
-      <c r="D44" s="78"/>
-    </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B45" s="80"/>
-      <c r="C45" s="78" t="s">
-        <v>174</v>
-      </c>
-      <c r="D45" s="78"/>
-    </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B46" s="80"/>
-      <c r="C46" s="78" t="s">
-        <v>175</v>
-      </c>
-      <c r="D46" s="78"/>
-    </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B47" s="31" t="s">
-        <v>3</v>
-      </c>
-      <c r="C47" s="77" t="s">
-        <v>176</v>
-      </c>
-      <c r="D47" s="77"/>
-    </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B48" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="C48" s="25" t="s">
-        <v>149</v>
-      </c>
-      <c r="D48" s="25"/>
-    </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B49" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="C49" s="78" t="s">
+      <c r="C59" s="75" t="s">
         <v>177</v>
       </c>
-      <c r="D49" s="78"/>
-    </row>
-    <row r="50" spans="2:4" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B50" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="79" t="s">
-        <v>178</v>
-      </c>
-      <c r="D50" s="76"/>
-    </row>
-    <row r="51" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B51" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="C51" s="77" t="s">
-        <v>179</v>
-      </c>
-      <c r="D51" s="77"/>
-    </row>
-    <row r="52" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B52" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C52" s="76" t="s">
-        <v>180</v>
-      </c>
-      <c r="D52" s="76"/>
-    </row>
-    <row r="53" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B53" s="58" t="s">
-        <v>9</v>
-      </c>
-      <c r="C53" s="21" t="s">
-        <v>10</v>
-      </c>
-      <c r="D53" s="21" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="54" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B54" s="58"/>
-      <c r="C54" s="30" t="s">
-        <v>181</v>
-      </c>
-      <c r="D54" s="23" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="55" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B55" s="58"/>
-      <c r="C55" s="74" t="s">
-        <v>183</v>
-      </c>
-      <c r="D55" s="25" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="56" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B56" s="58"/>
-      <c r="C56" s="74"/>
-      <c r="D56" s="8" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="57" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B57" s="31" t="s">
-        <v>12</v>
-      </c>
-      <c r="C57" s="76" t="s">
-        <v>186</v>
-      </c>
-      <c r="D57" s="76"/>
-    </row>
-    <row r="66" ht="64" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="69" ht="32" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="70" ht="32" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="D59" s="75"/>
+    </row>
+    <row r="68" ht="64" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="71" ht="32" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="72" ht="32" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="73" ht="32" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="42">
     <mergeCell ref="C7:D7"/>
@@ -3955,38 +3872,38 @@
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="B13:B17"/>
-    <mergeCell ref="C15:C17"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="B25:B27"/>
+    <mergeCell ref="B13:B18"/>
+    <mergeCell ref="C15:C18"/>
+    <mergeCell ref="C37:C38"/>
     <mergeCell ref="C25:D25"/>
     <mergeCell ref="C26:D26"/>
+    <mergeCell ref="B27:B29"/>
     <mergeCell ref="C27:D27"/>
-    <mergeCell ref="B53:B56"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="C37:D37"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C42:D42"/>
-    <mergeCell ref="C43:D43"/>
-    <mergeCell ref="B44:B46"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="B55:B58"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="B19:B21"/>
     <mergeCell ref="C44:D44"/>
     <mergeCell ref="C45:D45"/>
+    <mergeCell ref="B46:B48"/>
     <mergeCell ref="C46:D46"/>
-    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C48:D48"/>
     <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C31:D31"/>
     <mergeCell ref="C32:D32"/>
     <mergeCell ref="C33:D33"/>
-    <mergeCell ref="B34:B36"/>
-    <mergeCell ref="C57:D57"/>
-    <mergeCell ref="C55:C56"/>
-    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="B36:B38"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="C57:C58"/>
     <mergeCell ref="C49:D49"/>
-    <mergeCell ref="C50:D50"/>
     <mergeCell ref="C51:D51"/>
     <mergeCell ref="C52:D52"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="C54:D54"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4011,40 +3928,40 @@
       <c r="B2" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="62" t="s">
-        <v>89</v>
-      </c>
-      <c r="D2" s="63"/>
+      <c r="C2" s="61" t="s">
+        <v>85</v>
+      </c>
+      <c r="D2" s="62"/>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="62" t="s">
-        <v>188</v>
-      </c>
-      <c r="D3" s="63"/>
+      <c r="C3" s="61" t="s">
+        <v>178</v>
+      </c>
+      <c r="D3" s="62"/>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B4" s="69" t="s">
+      <c r="B4" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="62" t="s">
-        <v>189</v>
-      </c>
-      <c r="D4" s="63"/>
+      <c r="C4" s="61" t="s">
+        <v>179</v>
+      </c>
+      <c r="D4" s="62"/>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B5" s="70"/>
-      <c r="C5" s="72" t="s">
-        <v>190</v>
-      </c>
-      <c r="D5" s="73"/>
+      <c r="B5" s="69"/>
+      <c r="C5" s="71" t="s">
+        <v>180</v>
+      </c>
+      <c r="D5" s="72"/>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B6" s="71"/>
+      <c r="B6" s="70"/>
       <c r="C6" s="14" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="D6" s="15"/>
     </row>
@@ -4053,7 +3970,7 @@
         <v>3</v>
       </c>
       <c r="C7" s="44" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="D7" s="45"/>
     </row>
@@ -4062,7 +3979,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D8" s="11"/>
     </row>
@@ -4070,17 +3987,17 @@
       <c r="B9" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="75" t="s">
-        <v>241</v>
-      </c>
-      <c r="D9" s="63"/>
+      <c r="C9" s="74" t="s">
+        <v>226</v>
+      </c>
+      <c r="D9" s="62"/>
     </row>
     <row r="10" spans="2:4" ht="68" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="13" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="40" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="D10" s="41"/>
     </row>
@@ -4088,22 +4005,22 @@
       <c r="B11" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="64" t="s">
-        <v>196</v>
-      </c>
-      <c r="D11" s="65"/>
+      <c r="C11" s="63" t="s">
+        <v>186</v>
+      </c>
+      <c r="D11" s="64"/>
     </row>
     <row r="12" spans="2:4" ht="35" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B12" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="40" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D12" s="41"/>
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B13" s="80" t="s">
+      <c r="B13" s="79" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="21" t="s">
@@ -4114,121 +4031,121 @@
       </c>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B14" s="80"/>
+      <c r="B14" s="79"/>
       <c r="C14" s="27" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="D14" s="23" t="s">
-        <v>243</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B15" s="80"/>
-      <c r="C15" s="84" t="s">
-        <v>199</v>
+      <c r="B15" s="79"/>
+      <c r="C15" s="83" t="s">
+        <v>189</v>
       </c>
       <c r="D15" s="25" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B16" s="80"/>
-      <c r="C16" s="85"/>
+      <c r="B16" s="79"/>
+      <c r="C16" s="84"/>
       <c r="D16" s="25" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B17" s="80"/>
-      <c r="C17" s="85"/>
+      <c r="B17" s="79"/>
+      <c r="C17" s="84"/>
       <c r="D17" s="33" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
     </row>
     <row r="18" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="80"/>
-      <c r="C18" s="86"/>
+      <c r="B18" s="79"/>
+      <c r="C18" s="85"/>
       <c r="D18" s="25" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
     </row>
     <row r="19" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="58" t="s">
+      <c r="B19" s="57" t="s">
         <v>12</v>
       </c>
       <c r="C19" s="40" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="D19" s="41"/>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B20" s="58"/>
+      <c r="B20" s="57"/>
       <c r="C20" s="40" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="D20" s="41"/>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B21" s="58"/>
-      <c r="C21" s="87" t="s">
-        <v>206</v>
-      </c>
-      <c r="D21" s="87"/>
+      <c r="B21" s="57"/>
+      <c r="C21" s="86" t="s">
+        <v>196</v>
+      </c>
+      <c r="D21" s="86"/>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B24" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C24" s="62" t="s">
-        <v>207</v>
-      </c>
-      <c r="D24" s="63"/>
+      <c r="C24" s="61" t="s">
+        <v>197</v>
+      </c>
+      <c r="D24" s="62"/>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B25" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C25" s="62" t="s">
-        <v>208</v>
-      </c>
-      <c r="D25" s="63"/>
+      <c r="C25" s="61" t="s">
+        <v>198</v>
+      </c>
+      <c r="D25" s="62"/>
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B26" s="69" t="s">
+      <c r="B26" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="C26" s="62" t="s">
-        <v>209</v>
-      </c>
-      <c r="D26" s="63"/>
+      <c r="C26" s="61" t="s">
+        <v>199</v>
+      </c>
+      <c r="D26" s="62"/>
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B27" s="70"/>
-      <c r="C27" s="62" t="s">
-        <v>210</v>
-      </c>
-      <c r="D27" s="63"/>
+      <c r="B27" s="69"/>
+      <c r="C27" s="61" t="s">
+        <v>200</v>
+      </c>
+      <c r="D27" s="62"/>
     </row>
     <row r="28" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B28" s="71"/>
-      <c r="C28" s="62"/>
-      <c r="D28" s="63"/>
+      <c r="B28" s="70"/>
+      <c r="C28" s="61"/>
+      <c r="D28" s="62"/>
     </row>
     <row r="29" spans="2:4" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B29" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="C29" s="64" t="s">
-        <v>211</v>
-      </c>
-      <c r="D29" s="65"/>
+      <c r="C29" s="63" t="s">
+        <v>201</v>
+      </c>
+      <c r="D29" s="64"/>
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B30" s="13" t="s">
         <v>4</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D30" s="11"/>
     </row>
@@ -4236,10 +4153,10 @@
       <c r="B31" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C31" s="62" t="s">
-        <v>212</v>
-      </c>
-      <c r="D31" s="63"/>
+      <c r="C31" s="61" t="s">
+        <v>202</v>
+      </c>
+      <c r="D31" s="62"/>
     </row>
     <row r="32" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B32" s="13" t="s">
@@ -4254,22 +4171,22 @@
       <c r="B33" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C33" s="64" t="s">
-        <v>213</v>
-      </c>
-      <c r="D33" s="65"/>
+      <c r="C33" s="63" t="s">
+        <v>203</v>
+      </c>
+      <c r="D33" s="64"/>
     </row>
     <row r="34" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B34" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C34" s="40" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="D34" s="41"/>
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B35" s="69" t="s">
+      <c r="B35" s="68" t="s">
         <v>9</v>
       </c>
       <c r="C35" s="18" t="s">
@@ -4280,34 +4197,34 @@
       </c>
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B36" s="70"/>
-      <c r="C36" s="66" t="s">
-        <v>215</v>
+      <c r="B36" s="69"/>
+      <c r="C36" s="65" t="s">
+        <v>205</v>
       </c>
       <c r="D36" s="20" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B37" s="70"/>
-      <c r="C37" s="68"/>
+      <c r="B37" s="69"/>
+      <c r="C37" s="67"/>
       <c r="D37" s="20" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
     </row>
     <row r="38" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B38" s="69" t="s">
+      <c r="B38" s="68" t="s">
         <v>12</v>
       </c>
       <c r="C38" s="40" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="D38" s="41"/>
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B39" s="71"/>
+      <c r="B39" s="70"/>
       <c r="C39" s="19" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="D39" s="19"/>
     </row>
@@ -4315,55 +4232,55 @@
       <c r="B43" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C43" s="62" t="s">
-        <v>193</v>
-      </c>
-      <c r="D43" s="63"/>
-    </row>
-    <row r="44" spans="2:4" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C43" s="61" t="s">
+        <v>183</v>
+      </c>
+      <c r="D43" s="62"/>
+    </row>
+    <row r="44" spans="2:4" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B44" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C44" s="62" t="s">
-        <v>219</v>
-      </c>
-      <c r="D44" s="63"/>
+      <c r="C44" s="61" t="s">
+        <v>209</v>
+      </c>
+      <c r="D44" s="62"/>
     </row>
     <row r="45" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B45" s="69" t="s">
+      <c r="B45" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="C45" s="62" t="s">
-        <v>220</v>
-      </c>
-      <c r="D45" s="63"/>
+      <c r="C45" s="61" t="s">
+        <v>210</v>
+      </c>
+      <c r="D45" s="62"/>
     </row>
     <row r="46" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B46" s="70"/>
+      <c r="B46" s="69"/>
       <c r="C46" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
     </row>
     <row r="47" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B47" s="71"/>
-      <c r="C47" s="72"/>
-      <c r="D47" s="73"/>
+      <c r="B47" s="70"/>
+      <c r="C47" s="71"/>
+      <c r="D47" s="72"/>
     </row>
     <row r="48" spans="2:4" ht="80" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B48" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="C48" s="64" t="s">
-        <v>221</v>
-      </c>
-      <c r="D48" s="65"/>
+      <c r="C48" s="63" t="s">
+        <v>211</v>
+      </c>
+      <c r="D48" s="64"/>
     </row>
     <row r="49" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B49" s="13" t="s">
         <v>4</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="D49" s="11"/>
     </row>
@@ -4371,17 +4288,17 @@
       <c r="B50" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C50" s="62" t="s">
-        <v>225</v>
-      </c>
-      <c r="D50" s="63"/>
+      <c r="C50" s="61" t="s">
+        <v>215</v>
+      </c>
+      <c r="D50" s="62"/>
     </row>
     <row r="51" spans="2:4" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B51" s="13" t="s">
         <v>6</v>
       </c>
       <c r="C51" s="40" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="D51" s="41"/>
     </row>
@@ -4389,22 +4306,22 @@
       <c r="B52" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C52" s="64" t="s">
-        <v>223</v>
-      </c>
-      <c r="D52" s="65"/>
+      <c r="C52" s="63" t="s">
+        <v>213</v>
+      </c>
+      <c r="D52" s="64"/>
     </row>
     <row r="53" spans="2:4" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B53" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C53" s="40" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="D53" s="41"/>
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B54" s="69" t="s">
+      <c r="B54" s="68" t="s">
         <v>9</v>
       </c>
       <c r="C54" s="18" t="s">
@@ -4415,73 +4332,73 @@
       </c>
     </row>
     <row r="55" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B55" s="70"/>
-      <c r="C55" s="74" t="s">
-        <v>274</v>
+      <c r="B55" s="69"/>
+      <c r="C55" s="73" t="s">
+        <v>229</v>
       </c>
       <c r="D55" s="23" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
     </row>
     <row r="56" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B56" s="70"/>
-      <c r="C56" s="74"/>
+      <c r="B56" s="69"/>
+      <c r="C56" s="73"/>
       <c r="D56" s="23" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
     </row>
     <row r="57" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B57" s="70"/>
-      <c r="C57" s="66" t="s">
-        <v>231</v>
+      <c r="B57" s="69"/>
+      <c r="C57" s="65" t="s">
+        <v>221</v>
       </c>
       <c r="D57" s="19" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
     </row>
     <row r="58" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B58" s="70"/>
-      <c r="C58" s="67"/>
+      <c r="B58" s="69"/>
+      <c r="C58" s="66"/>
       <c r="D58" s="34" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B59" s="82"/>
-      <c r="C59" s="68"/>
+      <c r="B59" s="81"/>
+      <c r="C59" s="67"/>
       <c r="D59" s="35" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="60" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B60" s="80" t="s">
+      <c r="B60" s="79" t="s">
         <v>12</v>
       </c>
-      <c r="C60" s="62" t="s">
-        <v>168</v>
-      </c>
-      <c r="D60" s="83"/>
+      <c r="C60" s="61" t="s">
+        <v>160</v>
+      </c>
+      <c r="D60" s="82"/>
     </row>
     <row r="61" spans="2:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B61" s="80"/>
+      <c r="B61" s="79"/>
       <c r="C61" s="40" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="D61" s="41"/>
     </row>
     <row r="62" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B62" s="80"/>
-      <c r="C62" s="62" t="s">
-        <v>232</v>
-      </c>
-      <c r="D62" s="83"/>
+      <c r="B62" s="79"/>
+      <c r="C62" s="61" t="s">
+        <v>222</v>
+      </c>
+      <c r="D62" s="82"/>
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B63" s="80"/>
-      <c r="C63" s="62" t="s">
-        <v>233</v>
-      </c>
-      <c r="D63" s="83"/>
+      <c r="B63" s="79"/>
+      <c r="C63" s="61" t="s">
+        <v>223</v>
+      </c>
+      <c r="D63" s="82"/>
     </row>
   </sheetData>
   <mergeCells count="49">
@@ -4540,12 +4457,12 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65070C85-AA9C-7748-88E8-A7770308B2BD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D0D9413-24B7-774D-9777-26607EE3F2AA}">
   <dimension ref="A1:D73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="18.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="57.33203125" customWidth="1"/>
+    <col min="3" max="3" width="49.6640625" customWidth="1"/>
     <col min="4" max="4" width="86.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4560,44 +4477,44 @@
       <c r="B2" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="62" t="s">
-        <v>187</v>
-      </c>
-      <c r="D2" s="63"/>
+      <c r="C2" s="61" t="s">
+        <v>230</v>
+      </c>
+      <c r="D2" s="62"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="11"/>
       <c r="B3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="62" t="s">
-        <v>236</v>
-      </c>
-      <c r="D3" s="63"/>
+      <c r="C3" s="61" t="s">
+        <v>233</v>
+      </c>
+      <c r="D3" s="62"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="11"/>
-      <c r="B4" s="69" t="s">
+      <c r="B4" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="62" t="s">
-        <v>237</v>
-      </c>
-      <c r="D4" s="63"/>
+      <c r="C4" s="61" t="s">
+        <v>234</v>
+      </c>
+      <c r="D4" s="62"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="11"/>
-      <c r="B5" s="70"/>
-      <c r="C5" s="72" t="s">
-        <v>190</v>
-      </c>
-      <c r="D5" s="73"/>
+      <c r="B5" s="69"/>
+      <c r="C5" s="71" t="s">
+        <v>180</v>
+      </c>
+      <c r="D5" s="72"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="11"/>
-      <c r="B6" s="71"/>
+      <c r="B6" s="70"/>
       <c r="C6" s="14" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="D6" s="15"/>
     </row>
@@ -4606,10 +4523,10 @@
       <c r="B7" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="64" t="s">
-        <v>259</v>
-      </c>
-      <c r="D7" s="65"/>
+      <c r="C7" s="63" t="s">
+        <v>251</v>
+      </c>
+      <c r="D7" s="64"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="11"/>
@@ -4617,7 +4534,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>15</v>
+        <v>231</v>
       </c>
       <c r="D8" s="11"/>
     </row>
@@ -4626,10 +4543,10 @@
       <c r="B9" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="62" t="s">
-        <v>242</v>
-      </c>
-      <c r="D9" s="63"/>
+      <c r="C9" s="61" t="s">
+        <v>282</v>
+      </c>
+      <c r="D9" s="62"/>
     </row>
     <row r="10" spans="1:4" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="11"/>
@@ -4637,19 +4554,19 @@
         <v>6</v>
       </c>
       <c r="C10" s="40" t="s">
-        <v>306</v>
+        <v>253</v>
       </c>
       <c r="D10" s="41"/>
     </row>
-    <row r="11" spans="1:4" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" ht="71" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="11"/>
       <c r="B11" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="64" t="s">
-        <v>239</v>
-      </c>
-      <c r="D11" s="65"/>
+      <c r="C11" s="63" t="s">
+        <v>252</v>
+      </c>
+      <c r="D11" s="64"/>
     </row>
     <row r="12" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="11"/>
@@ -4657,13 +4574,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="40" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="D12" s="41"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="11"/>
-      <c r="B13" s="69" t="s">
+      <c r="B13" s="68" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="18" t="s">
@@ -4675,94 +4592,95 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="11"/>
-      <c r="B14" s="70"/>
+      <c r="B14" s="69"/>
       <c r="C14" s="32" t="s">
-        <v>245</v>
-      </c>
-      <c r="D14" s="20" t="s">
-        <v>244</v>
+        <v>236</v>
+      </c>
+      <c r="D14" s="23" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="11"/>
-      <c r="B15" s="70"/>
-      <c r="C15" s="84" t="s">
-        <v>246</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>312</v>
+      <c r="B15" s="69"/>
+      <c r="C15" s="65" t="s">
+        <v>232</v>
+      </c>
+      <c r="D15" s="25" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="11"/>
-      <c r="B16" s="70"/>
-      <c r="C16" s="85"/>
-      <c r="D16" s="19" t="s">
-        <v>260</v>
+      <c r="B16" s="69"/>
+      <c r="C16" s="66"/>
+      <c r="D16" s="25" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="11"/>
-      <c r="B17" s="70"/>
-      <c r="C17" s="85"/>
-      <c r="D17" s="19" t="s">
-        <v>311</v>
+      <c r="B17" s="69"/>
+      <c r="C17" s="66"/>
+      <c r="D17" s="25" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="11"/>
-      <c r="B18" s="70"/>
-      <c r="C18" s="85"/>
-      <c r="D18" s="34" t="s">
-        <v>261</v>
+      <c r="B18" s="69"/>
+      <c r="C18" s="66"/>
+      <c r="D18" s="25" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="11"/>
-      <c r="B19" s="82"/>
-      <c r="C19" s="86"/>
-      <c r="D19" s="35" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B19" s="81"/>
+      <c r="C19" s="67"/>
+      <c r="D19" s="25" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="11"/>
-      <c r="B20" s="59" t="s">
+      <c r="B20" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="27" t="s">
-        <v>313</v>
-      </c>
-      <c r="D20" s="25"/>
+      <c r="C20" s="75" t="s">
+        <v>192</v>
+      </c>
+      <c r="D20" s="75"/>
     </row>
     <row r="21" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="11"/>
-      <c r="B21" s="60"/>
-      <c r="C21" s="76" t="s">
-        <v>263</v>
-      </c>
-      <c r="D21" s="76"/>
+      <c r="B21" s="59"/>
+      <c r="C21" s="75" t="s">
+        <v>238</v>
+      </c>
+      <c r="D21" s="75"/>
     </row>
     <row r="22" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="11"/>
-      <c r="B22" s="60"/>
-      <c r="C22" s="76" t="s">
-        <v>314</v>
-      </c>
-      <c r="D22" s="76"/>
+      <c r="B22" s="59"/>
+      <c r="C22" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="D22" s="25"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="11"/>
-      <c r="B23" s="61"/>
-      <c r="C23" s="62" t="s">
-        <v>264</v>
-      </c>
-      <c r="D23" s="83"/>
+      <c r="B23" s="60"/>
+      <c r="C23" s="77" t="s">
+        <v>228</v>
+      </c>
+      <c r="D23" s="77"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="11"/>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="11"/>
@@ -4775,56 +4693,54 @@
       <c r="B26" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C26" s="62" t="s">
-        <v>247</v>
-      </c>
-      <c r="D26" s="63"/>
+      <c r="C26" s="61" t="s">
+        <v>239</v>
+      </c>
+      <c r="D26" s="62"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="11"/>
       <c r="B27" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C27" s="62" t="s">
-        <v>248</v>
-      </c>
-      <c r="D27" s="63"/>
+      <c r="C27" s="61" t="s">
+        <v>240</v>
+      </c>
+      <c r="D27" s="62"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="11"/>
-      <c r="B28" s="69" t="s">
+      <c r="B28" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="C28" s="62" t="s">
-        <v>250</v>
-      </c>
-      <c r="D28" s="63"/>
+      <c r="C28" s="61" t="s">
+        <v>241</v>
+      </c>
+      <c r="D28" s="62"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="11"/>
-      <c r="B29" s="70"/>
-      <c r="C29" s="62" t="s">
-        <v>251</v>
-      </c>
-      <c r="D29" s="63"/>
+      <c r="B29" s="69"/>
+      <c r="C29" s="61" t="s">
+        <v>242</v>
+      </c>
+      <c r="D29" s="62"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="11"/>
-      <c r="B30" s="71"/>
-      <c r="C30" s="62" t="s">
-        <v>236</v>
-      </c>
-      <c r="D30" s="63"/>
+      <c r="B30" s="70"/>
+      <c r="C30" s="61"/>
+      <c r="D30" s="62"/>
     </row>
     <row r="31" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="11"/>
       <c r="B31" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="C31" s="64" t="s">
-        <v>252</v>
-      </c>
-      <c r="D31" s="65"/>
+      <c r="C31" s="63" t="s">
+        <v>243</v>
+      </c>
+      <c r="D31" s="64"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="11"/>
@@ -4832,7 +4748,7 @@
         <v>4</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="D32" s="11"/>
     </row>
@@ -4841,10 +4757,10 @@
       <c r="B33" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C33" s="62" t="s">
-        <v>253</v>
-      </c>
-      <c r="D33" s="63"/>
+      <c r="C33" s="61" t="s">
+        <v>258</v>
+      </c>
+      <c r="D33" s="62"/>
     </row>
     <row r="34" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="11"/>
@@ -4861,10 +4777,10 @@
       <c r="B35" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C35" s="64" t="s">
-        <v>254</v>
-      </c>
-      <c r="D35" s="65"/>
+      <c r="C35" s="63" t="s">
+        <v>244</v>
+      </c>
+      <c r="D35" s="64"/>
     </row>
     <row r="36" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="11"/>
@@ -4872,13 +4788,13 @@
         <v>8</v>
       </c>
       <c r="C36" s="40" t="s">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="D36" s="41"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="11"/>
-      <c r="B37" s="69" t="s">
+      <c r="B37" s="68" t="s">
         <v>9</v>
       </c>
       <c r="C37" s="18" t="s">
@@ -4890,37 +4806,37 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="11"/>
-      <c r="B38" s="70"/>
-      <c r="C38" s="66" t="s">
-        <v>266</v>
+      <c r="B38" s="69"/>
+      <c r="C38" s="65" t="s">
+        <v>246</v>
       </c>
       <c r="D38" s="20" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" s="11"/>
-      <c r="B39" s="82"/>
-      <c r="C39" s="68"/>
+      <c r="B39" s="81"/>
+      <c r="C39" s="67"/>
       <c r="D39" s="20" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="11"/>
-      <c r="B40" s="69" t="s">
+      <c r="B40" s="68" t="s">
         <v>12</v>
       </c>
       <c r="C40" s="40" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="D40" s="41"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" s="11"/>
-      <c r="B41" s="71"/>
+      <c r="B41" s="70"/>
       <c r="C41" s="19" t="s">
-        <v>169</v>
+        <v>249</v>
       </c>
       <c r="D41" s="19"/>
     </row>
@@ -4947,54 +4863,54 @@
       <c r="B45" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C45" s="62" t="s">
-        <v>238</v>
-      </c>
-      <c r="D45" s="63"/>
+      <c r="C45" s="61" t="s">
+        <v>282</v>
+      </c>
+      <c r="D45" s="62"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" s="11"/>
       <c r="B46" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C46" s="62" t="s">
-        <v>257</v>
-      </c>
-      <c r="D46" s="63"/>
+      <c r="C46" s="61" t="s">
+        <v>259</v>
+      </c>
+      <c r="D46" s="62"/>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" s="11"/>
-      <c r="B47" s="69" t="s">
+      <c r="B47" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="C47" s="62" t="s">
-        <v>258</v>
-      </c>
-      <c r="D47" s="63"/>
+      <c r="C47" s="61" t="s">
+        <v>260</v>
+      </c>
+      <c r="D47" s="62"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" s="11"/>
-      <c r="B48" s="70"/>
+      <c r="B48" s="69"/>
       <c r="C48" s="11" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="D48" s="11"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" s="11"/>
-      <c r="B49" s="71"/>
-      <c r="C49" s="72"/>
-      <c r="D49" s="73"/>
-    </row>
-    <row r="50" spans="1:4" ht="52" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B49" s="70"/>
+      <c r="C49" s="71"/>
+      <c r="D49" s="72"/>
+    </row>
+    <row r="50" spans="1:4" ht="49" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="11"/>
       <c r="B50" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="C50" s="64" t="s">
-        <v>268</v>
-      </c>
-      <c r="D50" s="65"/>
+      <c r="C50" s="63" t="s">
+        <v>262</v>
+      </c>
+      <c r="D50" s="64"/>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" s="11"/>
@@ -5002,7 +4918,7 @@
         <v>4</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D51" s="11"/>
     </row>
@@ -5011,18 +4927,18 @@
       <c r="B52" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C52" s="62" t="s">
-        <v>270</v>
-      </c>
-      <c r="D52" s="63"/>
-    </row>
-    <row r="53" spans="1:4" ht="59" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C52" s="61" t="s">
+        <v>291</v>
+      </c>
+      <c r="D52" s="62"/>
+    </row>
+    <row r="53" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="11"/>
       <c r="B53" s="13" t="s">
         <v>6</v>
       </c>
       <c r="C53" s="40" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="D53" s="41"/>
     </row>
@@ -5031,10 +4947,10 @@
       <c r="B54" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C54" s="64" t="s">
-        <v>272</v>
-      </c>
-      <c r="D54" s="65"/>
+      <c r="C54" s="63" t="s">
+        <v>265</v>
+      </c>
+      <c r="D54" s="64"/>
     </row>
     <row r="55" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="11"/>
@@ -5042,13 +4958,13 @@
         <v>8</v>
       </c>
       <c r="C55" s="40" t="s">
-        <v>273</v>
+        <v>250</v>
       </c>
       <c r="D55" s="41"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" s="11"/>
-      <c r="B56" s="69" t="s">
+      <c r="B56" s="68" t="s">
         <v>9</v>
       </c>
       <c r="C56" s="18" t="s">
@@ -5060,81 +4976,93 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" s="11"/>
-      <c r="B57" s="70"/>
-      <c r="C57" s="66" t="s">
-        <v>277</v>
+      <c r="B57" s="69"/>
+      <c r="C57" s="65" t="s">
+        <v>269</v>
       </c>
       <c r="D57" s="20" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" s="11"/>
-      <c r="B58" s="70"/>
-      <c r="C58" s="68"/>
+      <c r="B58" s="69"/>
+      <c r="C58" s="67"/>
       <c r="D58" s="20" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" s="11"/>
-      <c r="B59" s="70"/>
-      <c r="C59" s="66" t="s">
-        <v>276</v>
+      <c r="B59" s="69"/>
+      <c r="C59" s="65" t="s">
+        <v>267</v>
       </c>
       <c r="D59" s="19" t="s">
-        <v>279</v>
+        <v>295</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" s="11"/>
-      <c r="B60" s="70"/>
-      <c r="C60" s="67"/>
+      <c r="B60" s="69"/>
+      <c r="C60" s="66"/>
       <c r="D60" s="34" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" s="11"/>
-      <c r="B61" s="71"/>
-      <c r="C61" s="68"/>
+      <c r="B61" s="70"/>
+      <c r="C61" s="67"/>
       <c r="D61" s="35" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" s="11"/>
-      <c r="B62" s="88" t="s">
+      <c r="B62" s="87" t="s">
         <v>12</v>
       </c>
-      <c r="C62" s="62" t="s">
-        <v>168</v>
-      </c>
-      <c r="D62" s="63"/>
+      <c r="C62" s="61" t="s">
+        <v>160</v>
+      </c>
+      <c r="D62" s="62"/>
     </row>
     <row r="63" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="11"/>
-      <c r="B63" s="70"/>
+      <c r="B63" s="69"/>
       <c r="C63" s="40" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="D63" s="41"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" s="11"/>
-      <c r="B64" s="70"/>
-      <c r="C64" s="62" t="s">
-        <v>232</v>
-      </c>
-      <c r="D64" s="63"/>
+      <c r="B64" s="69"/>
+      <c r="C64" s="61" t="s">
+        <v>222</v>
+      </c>
+      <c r="D64" s="62"/>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" s="11"/>
-      <c r="B65" s="82"/>
-      <c r="C65" s="62" t="s">
-        <v>233</v>
-      </c>
-      <c r="D65" s="63"/>
+      <c r="B65" s="81"/>
+      <c r="C65" s="61" t="s">
+        <v>223</v>
+      </c>
+      <c r="D65" s="62"/>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A66" s="11"/>
+      <c r="B66" s="11"/>
+      <c r="C66" s="11"/>
+      <c r="D66" s="11"/>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A67" s="11"/>
+      <c r="B67" s="11"/>
+      <c r="C67" s="11"/>
+      <c r="D67" s="11"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" s="11"/>
@@ -5174,27 +5102,27 @@
     </row>
   </sheetData>
   <mergeCells count="49">
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="C62:D62"/>
     <mergeCell ref="B62:B65"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="C63:D63"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="C65:D65"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="B13:B19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="C23:D23"/>
     <mergeCell ref="C15:C19"/>
     <mergeCell ref="B20:B23"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="B4:B6"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
     <mergeCell ref="C26:D26"/>
     <mergeCell ref="C27:D27"/>
     <mergeCell ref="C28:D28"/>
@@ -5229,13 +5157,13 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D0D9413-24B7-774D-9777-26607EE3F2AA}">
-  <dimension ref="A1:D73"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65070C85-AA9C-7748-88E8-A7770308B2BD}">
+  <dimension ref="A1:D70"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="18.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="49.6640625" customWidth="1"/>
-    <col min="4" max="4" width="86.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="50.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="61" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
@@ -5249,56 +5177,54 @@
       <c r="B2" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="62" t="s">
-        <v>281</v>
-      </c>
-      <c r="D2" s="63"/>
+      <c r="C2" s="61" t="s">
+        <v>278</v>
+      </c>
+      <c r="D2" s="62"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="11"/>
       <c r="B3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="62" t="s">
-        <v>284</v>
-      </c>
-      <c r="D3" s="63"/>
+      <c r="C3" s="61" t="s">
+        <v>279</v>
+      </c>
+      <c r="D3" s="62"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="11"/>
-      <c r="B4" s="69" t="s">
+      <c r="B4" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="62" t="s">
-        <v>285</v>
-      </c>
-      <c r="D4" s="63"/>
+      <c r="C4" s="61" t="s">
+        <v>281</v>
+      </c>
+      <c r="D4" s="62"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="11"/>
-      <c r="B5" s="70"/>
-      <c r="C5" s="72" t="s">
-        <v>190</v>
-      </c>
-      <c r="D5" s="73"/>
+      <c r="B5" s="69"/>
+      <c r="C5" s="71" t="s">
+        <v>280</v>
+      </c>
+      <c r="D5" s="72"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="11"/>
-      <c r="B6" s="71"/>
-      <c r="C6" s="14" t="s">
-        <v>191</v>
-      </c>
+      <c r="B6" s="70"/>
+      <c r="C6" s="14"/>
       <c r="D6" s="15"/>
     </row>
-    <row r="7" spans="1:4" ht="64" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" ht="68" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="11"/>
       <c r="B7" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="64" t="s">
-        <v>303</v>
-      </c>
-      <c r="D7" s="65"/>
+      <c r="C7" s="63" t="s">
+        <v>296</v>
+      </c>
+      <c r="D7" s="64"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="11"/>
@@ -5306,7 +5232,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>282</v>
+        <v>231</v>
       </c>
       <c r="D8" s="11"/>
     </row>
@@ -5315,44 +5241,44 @@
       <c r="B9" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="62" t="s">
-        <v>286</v>
-      </c>
-      <c r="D9" s="63"/>
-    </row>
-    <row r="10" spans="1:4" ht="64" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C9" s="61" t="s">
+        <v>282</v>
+      </c>
+      <c r="D9" s="62"/>
+    </row>
+    <row r="10" spans="1:4" ht="63" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="11"/>
       <c r="B10" s="13" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="40" t="s">
-        <v>305</v>
+        <v>283</v>
       </c>
       <c r="D10" s="41"/>
     </row>
-    <row r="11" spans="1:4" ht="71" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="11"/>
       <c r="B11" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="64" t="s">
-        <v>304</v>
-      </c>
-      <c r="D11" s="65"/>
-    </row>
-    <row r="12" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C11" s="63" t="s">
+        <v>252</v>
+      </c>
+      <c r="D11" s="64"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="11"/>
       <c r="B12" s="12" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="40" t="s">
-        <v>287</v>
+        <v>235</v>
       </c>
       <c r="D12" s="41"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="11"/>
-      <c r="B13" s="69" t="s">
+      <c r="B13" s="68" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="18" t="s">
@@ -5364,465 +5290,459 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="11"/>
-      <c r="B14" s="70"/>
+      <c r="B14" s="69"/>
       <c r="C14" s="32" t="s">
-        <v>288</v>
-      </c>
-      <c r="D14" s="23" t="s">
-        <v>307</v>
+        <v>284</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="11"/>
-      <c r="B15" s="70"/>
-      <c r="C15" s="66" t="s">
-        <v>283</v>
-      </c>
-      <c r="D15" s="25" t="s">
-        <v>200</v>
+      <c r="B15" s="69"/>
+      <c r="C15" s="93"/>
+      <c r="D15" s="19" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="11"/>
-      <c r="B16" s="70"/>
-      <c r="C16" s="67"/>
-      <c r="D16" s="25" t="s">
-        <v>289</v>
+      <c r="B16" s="69"/>
+      <c r="C16" s="65" t="s">
+        <v>232</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="11"/>
-      <c r="B17" s="70"/>
-      <c r="C17" s="67"/>
-      <c r="D17" s="25" t="s">
-        <v>308</v>
+      <c r="B17" s="69"/>
+      <c r="C17" s="66"/>
+      <c r="D17" s="19" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="11"/>
       <c r="B18" s="70"/>
       <c r="C18" s="67"/>
-      <c r="D18" s="25" t="s">
-        <v>261</v>
+      <c r="D18" s="19" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="11"/>
-      <c r="B19" s="82"/>
-      <c r="C19" s="68"/>
-      <c r="D19" s="25" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="88" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="40" t="s">
+        <v>192</v>
+      </c>
+      <c r="D19" s="90"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="11"/>
-      <c r="B20" s="59" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" s="76" t="s">
-        <v>202</v>
-      </c>
-      <c r="D20" s="76"/>
-    </row>
-    <row r="21" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="89"/>
+      <c r="C20" s="61" t="s">
+        <v>223</v>
+      </c>
+      <c r="D20" s="82"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="11"/>
-      <c r="B21" s="60"/>
-      <c r="C21" s="76" t="s">
-        <v>290</v>
-      </c>
-      <c r="D21" s="76"/>
-    </row>
-    <row r="22" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="11"/>
-      <c r="B22" s="60"/>
-      <c r="C22" s="8" t="s">
-        <v>310</v>
-      </c>
-      <c r="D22" s="89"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="11"/>
-      <c r="B23" s="61"/>
-      <c r="C23" s="78" t="s">
-        <v>264</v>
-      </c>
-      <c r="D23" s="78"/>
+      <c r="B23" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C23" s="61" t="s">
+        <v>239</v>
+      </c>
+      <c r="D23" s="62"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="11"/>
-      <c r="B24" s="11"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
+      <c r="B24" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="61" t="s">
+        <v>287</v>
+      </c>
+      <c r="D24" s="62"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="11"/>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
+      <c r="B25" s="68" t="s">
+        <v>2</v>
+      </c>
+      <c r="C25" s="61" t="s">
+        <v>241</v>
+      </c>
+      <c r="D25" s="62"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="11"/>
-      <c r="B26" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C26" s="62" t="s">
-        <v>291</v>
-      </c>
-      <c r="D26" s="63"/>
+      <c r="B26" s="69"/>
+      <c r="C26" s="61" t="s">
+        <v>242</v>
+      </c>
+      <c r="D26" s="62"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="11"/>
-      <c r="B27" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C27" s="62" t="s">
-        <v>292</v>
-      </c>
-      <c r="D27" s="63"/>
+      <c r="B27" s="70"/>
+      <c r="C27" s="61"/>
+      <c r="D27" s="62"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="11"/>
-      <c r="B28" s="69" t="s">
-        <v>2</v>
-      </c>
-      <c r="C28" s="62" t="s">
-        <v>293</v>
-      </c>
-      <c r="D28" s="63"/>
+      <c r="B28" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="C28" s="63" t="s">
+        <v>243</v>
+      </c>
+      <c r="D28" s="64"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="11"/>
-      <c r="B29" s="70"/>
-      <c r="C29" s="62" t="s">
-        <v>294</v>
-      </c>
-      <c r="D29" s="63"/>
+      <c r="B29" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="D29" s="11"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="11"/>
-      <c r="B30" s="71"/>
-      <c r="C30" s="62"/>
-      <c r="D30" s="63"/>
-    </row>
-    <row r="31" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B30" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C30" s="61" t="s">
+        <v>258</v>
+      </c>
+      <c r="D30" s="62"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="11"/>
-      <c r="B31" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="C31" s="64" t="s">
-        <v>295</v>
-      </c>
-      <c r="D31" s="65"/>
+      <c r="B31" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="D31" s="41"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="11"/>
-      <c r="B32" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>282</v>
-      </c>
-      <c r="D32" s="11"/>
+      <c r="B32" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="63" t="s">
+        <v>244</v>
+      </c>
+      <c r="D32" s="64"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="11"/>
-      <c r="B33" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="C33" s="62" t="s">
-        <v>315</v>
-      </c>
-      <c r="D33" s="63"/>
-    </row>
-    <row r="34" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B33" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="40" t="s">
+        <v>245</v>
+      </c>
+      <c r="D33" s="41"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="11"/>
-      <c r="B34" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="40" t="s">
-        <v>14</v>
-      </c>
-      <c r="D34" s="41"/>
-    </row>
-    <row r="35" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B34" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="C34" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D34" s="18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="11"/>
-      <c r="B35" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="64" t="s">
-        <v>296</v>
-      </c>
-      <c r="D35" s="65"/>
-    </row>
-    <row r="36" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B35" s="69"/>
+      <c r="C35" s="65" t="s">
+        <v>246</v>
+      </c>
+      <c r="D35" s="20" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="11"/>
-      <c r="B36" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C36" s="40" t="s">
-        <v>297</v>
-      </c>
-      <c r="D36" s="41"/>
+      <c r="B36" s="70"/>
+      <c r="C36" s="67"/>
+      <c r="D36" s="20" t="s">
+        <v>248</v>
+      </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="11"/>
-      <c r="B37" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="C37" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="D37" s="18" t="s">
-        <v>11</v>
-      </c>
+      <c r="B37" s="87" t="s">
+        <v>12</v>
+      </c>
+      <c r="C37" s="40" t="s">
+        <v>160</v>
+      </c>
+      <c r="D37" s="41"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" s="11"/>
       <c r="B38" s="70"/>
-      <c r="C38" s="66" t="s">
-        <v>298</v>
-      </c>
-      <c r="D38" s="20" t="s">
-        <v>299</v>
-      </c>
+      <c r="C38" s="19" t="s">
+        <v>249</v>
+      </c>
+      <c r="D38" s="19"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" s="11"/>
-      <c r="B39" s="82"/>
-      <c r="C39" s="68"/>
-      <c r="D39" s="20" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" s="11"/>
-      <c r="B40" s="69" t="s">
-        <v>12</v>
-      </c>
-      <c r="C40" s="40" t="s">
-        <v>168</v>
-      </c>
-      <c r="D40" s="41"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="11"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" s="11"/>
-      <c r="B41" s="71"/>
-      <c r="C41" s="19" t="s">
-        <v>301</v>
-      </c>
-      <c r="D41" s="19"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="11"/>
+      <c r="D41" s="11"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" s="11"/>
-      <c r="B42" s="11"/>
-      <c r="C42" s="11"/>
-      <c r="D42" s="11"/>
+      <c r="B42" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C42" s="61" t="s">
+        <v>282</v>
+      </c>
+      <c r="D42" s="62"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" s="11"/>
-      <c r="B43" s="11"/>
-      <c r="C43" s="11"/>
-      <c r="D43" s="11"/>
+      <c r="B43" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C43" s="61" t="s">
+        <v>289</v>
+      </c>
+      <c r="D43" s="62"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" s="11"/>
-      <c r="B44" s="11"/>
-      <c r="C44" s="11"/>
-      <c r="D44" s="11"/>
+      <c r="B44" s="68" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="61" t="s">
+        <v>260</v>
+      </c>
+      <c r="D44" s="62"/>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" s="11"/>
-      <c r="B45" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C45" s="62" t="s">
-        <v>286</v>
-      </c>
-      <c r="D45" s="63"/>
+      <c r="B45" s="69"/>
+      <c r="C45" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="D45" s="11"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" s="11"/>
-      <c r="B46" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C46" s="62" t="s">
-        <v>316</v>
-      </c>
-      <c r="D46" s="63"/>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B46" s="70"/>
+      <c r="C46" s="71"/>
+      <c r="D46" s="72"/>
+    </row>
+    <row r="47" spans="1:4" ht="41" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="11"/>
-      <c r="B47" s="69" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="62" t="s">
-        <v>317</v>
-      </c>
-      <c r="D47" s="63"/>
+      <c r="B47" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="C47" s="63" t="s">
+        <v>290</v>
+      </c>
+      <c r="D47" s="64"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" s="11"/>
-      <c r="B48" s="70"/>
+      <c r="B48" s="13" t="s">
+        <v>4</v>
+      </c>
       <c r="C48" s="11" t="s">
-        <v>318</v>
+        <v>263</v>
       </c>
       <c r="D48" s="11"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" s="11"/>
-      <c r="B49" s="71"/>
-      <c r="C49" s="72"/>
-      <c r="D49" s="73"/>
-    </row>
-    <row r="50" spans="1:4" ht="49" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B49" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="C49" s="61" t="s">
+        <v>291</v>
+      </c>
+      <c r="D49" s="62"/>
+    </row>
+    <row r="50" spans="1:4" ht="31" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="11"/>
-      <c r="B50" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="C50" s="64" t="s">
-        <v>319</v>
-      </c>
-      <c r="D50" s="65"/>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B50" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="40" t="s">
+        <v>292</v>
+      </c>
+      <c r="D50" s="41"/>
+    </row>
+    <row r="51" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="11"/>
-      <c r="B51" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="C51" s="11" t="s">
-        <v>320</v>
-      </c>
-      <c r="D51" s="11"/>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B51" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="63" t="s">
+        <v>288</v>
+      </c>
+      <c r="D51" s="64"/>
+    </row>
+    <row r="52" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="11"/>
-      <c r="B52" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="C52" s="62" t="s">
-        <v>321</v>
-      </c>
-      <c r="D52" s="63"/>
-    </row>
-    <row r="53" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B52" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="C52" s="40" t="s">
+        <v>294</v>
+      </c>
+      <c r="D52" s="41"/>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" s="11"/>
-      <c r="B53" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C53" s="40" t="s">
-        <v>322</v>
-      </c>
-      <c r="D53" s="41"/>
-    </row>
-    <row r="54" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B53" s="68" t="s">
+        <v>9</v>
+      </c>
+      <c r="C53" s="18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D53" s="18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" s="11"/>
-      <c r="B54" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="C54" s="64" t="s">
-        <v>323</v>
-      </c>
-      <c r="D54" s="65"/>
-    </row>
-    <row r="55" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B54" s="69"/>
+      <c r="C54" s="65" t="s">
+        <v>269</v>
+      </c>
+      <c r="D54" s="20" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" s="11"/>
-      <c r="B55" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C55" s="40" t="s">
-        <v>302</v>
-      </c>
-      <c r="D55" s="41"/>
+      <c r="B55" s="69"/>
+      <c r="C55" s="91"/>
+      <c r="D55" s="20" t="s">
+        <v>266</v>
+      </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" s="11"/>
-      <c r="B56" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="C56" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="D56" s="18" t="s">
-        <v>11</v>
+      <c r="B56" s="69"/>
+      <c r="C56" s="92" t="s">
+        <v>267</v>
+      </c>
+      <c r="D56" s="19" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" s="11"/>
-      <c r="B57" s="70"/>
-      <c r="C57" s="66" t="s">
-        <v>327</v>
-      </c>
-      <c r="D57" s="20" t="s">
-        <v>328</v>
+      <c r="B57" s="69"/>
+      <c r="C57" s="66"/>
+      <c r="D57" s="34" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" s="11"/>
       <c r="B58" s="70"/>
-      <c r="C58" s="68"/>
-      <c r="D58" s="20" t="s">
-        <v>324</v>
+      <c r="C58" s="67"/>
+      <c r="D58" s="35" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" s="11"/>
-      <c r="B59" s="70"/>
-      <c r="C59" s="66" t="s">
-        <v>325</v>
-      </c>
-      <c r="D59" s="19" t="s">
-        <v>329</v>
-      </c>
+      <c r="B59" s="87" t="s">
+        <v>12</v>
+      </c>
+      <c r="C59" s="61" t="s">
+        <v>160</v>
+      </c>
+      <c r="D59" s="62"/>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" s="11"/>
-      <c r="B60" s="70"/>
-      <c r="C60" s="67"/>
-      <c r="D60" s="34" t="s">
-        <v>234</v>
-      </c>
+      <c r="B60" s="69"/>
+      <c r="C60" s="40" t="s">
+        <v>268</v>
+      </c>
+      <c r="D60" s="41"/>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" s="11"/>
-      <c r="B61" s="71"/>
-      <c r="C61" s="68"/>
-      <c r="D61" s="35" t="s">
-        <v>229</v>
-      </c>
+      <c r="B61" s="69"/>
+      <c r="C61" s="61" t="s">
+        <v>222</v>
+      </c>
+      <c r="D61" s="62"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" s="11"/>
-      <c r="B62" s="88" t="s">
-        <v>12</v>
-      </c>
-      <c r="C62" s="62" t="s">
-        <v>168</v>
-      </c>
-      <c r="D62" s="63"/>
-    </row>
-    <row r="63" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B62" s="70"/>
+      <c r="C62" s="61" t="s">
+        <v>223</v>
+      </c>
+      <c r="D62" s="62"/>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" s="11"/>
-      <c r="B63" s="70"/>
-      <c r="C63" s="40" t="s">
-        <v>326</v>
-      </c>
-      <c r="D63" s="41"/>
+      <c r="B63" s="11"/>
+      <c r="C63" s="11"/>
+      <c r="D63" s="11"/>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" s="11"/>
-      <c r="B64" s="70"/>
-      <c r="C64" s="62" t="s">
-        <v>232</v>
-      </c>
-      <c r="D64" s="63"/>
+      <c r="B64" s="11"/>
+      <c r="C64" s="11"/>
+      <c r="D64" s="11"/>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" s="11"/>
-      <c r="B65" s="82"/>
-      <c r="C65" s="62" t="s">
-        <v>233</v>
-      </c>
-      <c r="D65" s="63"/>
+      <c r="B65" s="11"/>
+      <c r="C65" s="11"/>
+      <c r="D65" s="11"/>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" s="11"/>
@@ -5854,75 +5774,56 @@
       <c r="C70" s="11"/>
       <c r="D70" s="11"/>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A71" s="11"/>
-      <c r="B71" s="11"/>
-      <c r="C71" s="11"/>
-      <c r="D71" s="11"/>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A72" s="11"/>
-      <c r="B72" s="11"/>
-      <c r="C72" s="11"/>
-      <c r="D72" s="11"/>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A73" s="11"/>
-      <c r="B73" s="11"/>
-      <c r="C73" s="11"/>
-      <c r="D73" s="11"/>
-    </row>
   </sheetData>
-  <mergeCells count="49">
-    <mergeCell ref="C65:D65"/>
-    <mergeCell ref="C64:D64"/>
-    <mergeCell ref="C63:D63"/>
+  <mergeCells count="48">
+    <mergeCell ref="B59:B62"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="C61:D61"/>
     <mergeCell ref="C62:D62"/>
-    <mergeCell ref="B62:B65"/>
     <mergeCell ref="C7:D7"/>
-    <mergeCell ref="B13:B19"/>
-    <mergeCell ref="C15:C19"/>
-    <mergeCell ref="B20:B23"/>
+    <mergeCell ref="B13:B18"/>
     <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C19:D19"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="B4:B6"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
     <mergeCell ref="C26:D26"/>
+    <mergeCell ref="B25:B27"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="B34:B36"/>
+    <mergeCell ref="C35:C36"/>
     <mergeCell ref="C27:D27"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="B28:B30"/>
+    <mergeCell ref="C30:D30"/>
     <mergeCell ref="C31:D31"/>
-    <mergeCell ref="C36:D36"/>
-    <mergeCell ref="B37:B39"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C57:C58"/>
-    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="C42:D42"/>
+    <mergeCell ref="C43:D43"/>
+    <mergeCell ref="C44:D44"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="B44:B46"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="C52:D52"/>
+    <mergeCell ref="B53:B58"/>
     <mergeCell ref="C46:D46"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="B47:B49"/>
+    <mergeCell ref="C49:D49"/>
     <mergeCell ref="C50:D50"/>
-    <mergeCell ref="C55:D55"/>
-    <mergeCell ref="B56:B61"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="C52:D52"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="C54:D54"/>
-    <mergeCell ref="C59:C61"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="C56:C58"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Diagram/UseCaseDescription.xlsx
+++ b/Diagram/UseCaseDescription.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/paultsai/Desktop/SLC/TPA/Desktop/TPA-Desktop/Diagram/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFB371F4-B3BB-1B46-A87C-4F5B9CF81B83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A50D3A0-03F6-CB4B-8FB5-3B82D6D7C54F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="7" xr2:uid="{2183EE87-2FE0-1848-A8EC-EAF6DA5552F2}"/>
+    <workbookView minimized="1" xWindow="-20" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="7" xr2:uid="{2183EE87-2FE0-1848-A8EC-EAF6DA5552F2}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Add New Menu Item" sheetId="1" r:id="rId1"/>
@@ -1220,7 +1220,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1476,9 +1476,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5301,7 +5298,9 @@
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="11"/>
       <c r="B15" s="69"/>
-      <c r="C15" s="93"/>
+      <c r="C15" s="83" t="s">
+        <v>232</v>
+      </c>
       <c r="D15" s="19" t="s">
         <v>190</v>
       </c>
@@ -5309,9 +5308,7 @@
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="11"/>
       <c r="B16" s="69"/>
-      <c r="C16" s="65" t="s">
-        <v>232</v>
-      </c>
+      <c r="C16" s="84"/>
       <c r="D16" s="19" t="s">
         <v>300</v>
       </c>
@@ -5319,7 +5316,7 @@
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="11"/>
       <c r="B17" s="69"/>
-      <c r="C17" s="66"/>
+      <c r="C17" s="84"/>
       <c r="D17" s="19" t="s">
         <v>285</v>
       </c>
@@ -5327,7 +5324,7 @@
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="11"/>
       <c r="B18" s="70"/>
-      <c r="C18" s="67"/>
+      <c r="C18" s="85"/>
       <c r="D18" s="19" t="s">
         <v>286</v>
       </c>
@@ -5784,13 +5781,13 @@
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="B13:B18"/>
     <mergeCell ref="C20:D20"/>
-    <mergeCell ref="C16:C18"/>
     <mergeCell ref="B19:B20"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C15:C18"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="B4:B6"/>
